--- a/tables.xlsx
+++ b/tables.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Docentes activos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$575</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$581</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J575"/>
+  <dimension ref="A1:J581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21059,7 +21059,7 @@
     <row r="571" ht="16" customHeight="1">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040648386</t>
+          <t>2-s2.0-105040384895</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="I571" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J571" s="4" t="inlineStr">
@@ -21095,7 +21095,7 @@
     <row r="572" ht="16" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040813266</t>
+          <t>2-s2.0-105040648386</t>
         </is>
       </c>
       <c r="B572" s="3" t="n">
@@ -21119,19 +21119,19 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="573" ht="16" customHeight="1">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040999318</t>
+          <t>2-s2.0-105040720975</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr"/>
@@ -21147,7 +21147,7 @@
       <c r="F573" s="4" t="inlineStr"/>
       <c r="G573" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H573" s="4" t="n">
@@ -21155,19 +21155,19 @@
       </c>
       <c r="I573" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J573" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="574" ht="16" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041022111</t>
+          <t>2-s2.0-105040813266</t>
         </is>
       </c>
       <c r="B574" s="3" t="n">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr">
@@ -21203,7 +21203,7 @@
     <row r="575" ht="16" customHeight="1">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041142576</t>
+          <t>2-s2.0-105040833810</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -21219,25 +21219,241 @@
       <c r="F575" s="4" t="inlineStr"/>
       <c r="G575" s="4" t="inlineStr">
         <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H575" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I575" s="4" t="inlineStr">
+        <is>
+          <t>Miguel Efren Garces Prettel</t>
+        </is>
+      </c>
+      <c r="J575" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="16" customHeight="1">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105040999318</t>
+        </is>
+      </c>
+      <c r="B576" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C576" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr"/>
+      <c r="E576" s="3" t="inlineStr"/>
+      <c r="F576" s="2" t="inlineStr"/>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H575" s="4" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="I575" s="4" t="inlineStr">
+      <c r="H576" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Luis del Rio Cortina</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="16" customHeight="1">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105041019868</t>
+        </is>
+      </c>
+      <c r="B577" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C577" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D577" s="4" t="inlineStr"/>
+      <c r="E577" s="5" t="inlineStr"/>
+      <c r="F577" s="4" t="inlineStr"/>
+      <c r="G577" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H577" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I577" s="4" t="inlineStr">
+        <is>
+          <t>Luz Marina Gómez Hernández</t>
+        </is>
+      </c>
+      <c r="J577" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="16" customHeight="1">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105041022111</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C578" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr"/>
+      <c r="E578" s="3" t="inlineStr"/>
+      <c r="F578" s="2" t="inlineStr"/>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>Diana Carolina Rubiano Labrador</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="16" customHeight="1">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105041142576</t>
+        </is>
+      </c>
+      <c r="B579" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C579" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D579" s="4" t="inlineStr"/>
+      <c r="E579" s="5" t="inlineStr"/>
+      <c r="F579" s="4" t="inlineStr"/>
+      <c r="G579" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H579" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I579" s="4" t="inlineStr">
         <is>
           <t>David Sierra Porta</t>
         </is>
       </c>
-      <c r="J575" s="4" t="inlineStr">
+      <c r="J579" s="4" t="inlineStr">
         <is>
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
+    <row r="580" ht="16" customHeight="1">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105042109693</t>
+        </is>
+      </c>
+      <c r="B580" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C580" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr"/>
+      <c r="E580" s="3" t="inlineStr"/>
+      <c r="F580" s="2" t="inlineStr"/>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>Juan Carlos Martinez Santos</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="16" customHeight="1">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105042557607</t>
+        </is>
+      </c>
+      <c r="B581" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D581" s="4" t="inlineStr"/>
+      <c r="E581" s="5" t="inlineStr"/>
+      <c r="F581" s="4" t="inlineStr"/>
+      <c r="G581" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H581" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I581" s="4" t="inlineStr">
+        <is>
+          <t>Juan Carlos Martinez Santos</t>
+        </is>
+      </c>
+      <c r="J581" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J575"/>
+  <autoFilter ref="A1:J581"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21528,13 +21744,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>5</v>
@@ -21543,10 +21759,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>6</v>
@@ -21559,12 +21775,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -21671,10 +21887,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>122</v>
@@ -21689,7 +21905,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>14</v>
@@ -21702,7 +21918,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -21716,13 +21932,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>2</v>
@@ -21731,10 +21947,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>9</v>
@@ -21747,7 +21963,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22031,16 +22247,16 @@
       </c>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -22053,7 +22269,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -22411,7 +22627,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -22421,80 +22637,80 @@
       </c>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="H13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
@@ -22502,13 +22718,13 @@
         <v>20</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -22521,7 +22737,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Docentes activos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$584</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J581"/>
+  <dimension ref="A1:J584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="I395" s="4" t="inlineStr">
         <is>
-          <t>Carlos Rafael Payares Guevara; Hernando Rafael Altamar Mercado; Alberto Patiño Vanegas</t>
+          <t>Carlos Rafael Payares Guevara; Enrique Pereira Batista; Hernando Rafael Altamar Mercado; Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="J395" s="4" t="inlineStr">
@@ -21383,7 +21383,7 @@
     <row r="580" ht="16" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042109693</t>
+          <t>2-s2.0-105041927617</t>
         </is>
       </c>
       <c r="B580" s="3" t="n">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
       <c r="F580" s="2" t="inlineStr"/>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H580" s="2" t="n">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J580" s="2" t="inlineStr">
@@ -21419,7 +21419,7 @@
     <row r="581" ht="16" customHeight="1">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105042557607</t>
+          <t>2-s2.0-105042109693</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="I581" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J581" s="4" t="inlineStr">
@@ -21452,8 +21452,116 @@
         </is>
       </c>
     </row>
+    <row r="582" ht="16" customHeight="1">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105042557607</t>
+        </is>
+      </c>
+      <c r="B582" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C582" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr"/>
+      <c r="E582" s="3" t="inlineStr"/>
+      <c r="F582" s="2" t="inlineStr"/>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="16" customHeight="1">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105042877513</t>
+        </is>
+      </c>
+      <c r="B583" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C583" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D583" s="4" t="inlineStr"/>
+      <c r="E583" s="5" t="inlineStr"/>
+      <c r="F583" s="4" t="inlineStr"/>
+      <c r="G583" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H583" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I583" s="4" t="inlineStr">
+        <is>
+          <t>Cesar Augusto Viloria Nuñez</t>
+        </is>
+      </c>
+      <c r="J583" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="16" customHeight="1">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105043654106</t>
+        </is>
+      </c>
+      <c r="B584" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C584" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr"/>
+      <c r="E584" s="3" t="inlineStr"/>
+      <c r="F584" s="2" t="inlineStr"/>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J581"/>
+  <autoFilter ref="A1:J584"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21744,13 +21852,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>5</v>
@@ -21762,7 +21870,7 @@
         <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>6</v>
@@ -21775,12 +21883,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -21932,13 +22040,13 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>2</v>
@@ -21950,7 +22058,7 @@
         <v>44</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>9</v>
@@ -21963,7 +22071,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22286,16 +22394,16 @@
       </c>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0</v>
@@ -22308,7 +22416,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -22354,51 +22462,51 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -22406,26 +22514,26 @@
         <v>32</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -22637,16 +22745,16 @@
       </c>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -22659,7 +22767,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Docentes activos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$584</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$587</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J584"/>
+  <dimension ref="A1:J587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21560,8 +21560,116 @@
         </is>
       </c>
     </row>
+    <row r="585" ht="16" customHeight="1">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105044659449</t>
+        </is>
+      </c>
+      <c r="B585" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D585" s="4" t="inlineStr"/>
+      <c r="E585" s="5" t="inlineStr"/>
+      <c r="F585" s="4" t="inlineStr"/>
+      <c r="G585" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H585" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I585" s="4" t="inlineStr">
+        <is>
+          <t>Efraín Andrés Rodríguez Gasca</t>
+        </is>
+      </c>
+      <c r="J585" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="16" customHeight="1">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105044699156</t>
+        </is>
+      </c>
+      <c r="B586" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C586" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr"/>
+      <c r="E586" s="3" t="inlineStr"/>
+      <c r="F586" s="2" t="inlineStr"/>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="16" customHeight="1">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105044735313</t>
+        </is>
+      </c>
+      <c r="B587" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D587" s="4" t="inlineStr"/>
+      <c r="E587" s="5" t="inlineStr"/>
+      <c r="F587" s="4" t="inlineStr"/>
+      <c r="G587" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H587" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I587" s="4" t="inlineStr">
+        <is>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
+        </is>
+      </c>
+      <c r="J587" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J584"/>
+  <autoFilter ref="A1:J587"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21852,10 +21960,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>9</v>
@@ -21867,13 +21975,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>13</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1</v>
@@ -21883,12 +21991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -21995,10 +22103,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>122</v>
@@ -22010,7 +22118,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>26</v>
@@ -22026,7 +22134,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -22040,10 +22148,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>126</v>
@@ -22055,7 +22163,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>27</v>
@@ -22071,7 +22179,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22085,10 +22193,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -22106,7 +22214,7 @@
         <v>17</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>14</v>
@@ -22116,7 +22224,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -22472,13 +22580,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>9</v>
@@ -22494,7 +22602,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Docentes activos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$587</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$588</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J587"/>
+  <dimension ref="A1:J588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13067,7 +13067,7 @@
     <row r="349" ht="16" customHeight="1">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105007361101</t>
+          <t>2-s2.0-105007728920</t>
         </is>
       </c>
       <c r="B349" s="5" t="n">
@@ -13091,19 +13091,19 @@
       </c>
       <c r="I349" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Carlos Rafael Payares Guevara; Alberto Patiño Vanegas; Enrique Pereira Batista</t>
         </is>
       </c>
       <c r="J349" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="350" ht="16" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105007728920</t>
+          <t>2-s2.0-105008182277</t>
         </is>
       </c>
       <c r="B350" s="3" t="n">
@@ -13127,19 +13127,19 @@
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>Carlos Rafael Payares Guevara; Alberto Patiño Vanegas; Enrique Pereira Batista</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="351" ht="16" customHeight="1">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105008182277</t>
+          <t>2-s2.0-105008430466</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
@@ -13155,7 +13155,7 @@
       <c r="F351" s="4" t="inlineStr"/>
       <c r="G351" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H351" s="4" t="n">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="I351" s="4" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J351" s="4" t="inlineStr">
@@ -13175,7 +13175,7 @@
     <row r="352" ht="16" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105008430466</t>
+          <t>2-s2.0-105009263283</t>
         </is>
       </c>
       <c r="B352" s="3" t="n">
@@ -13199,19 +13199,19 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="353" ht="16" customHeight="1">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105009263283</t>
+          <t>2-s2.0-105010266217</t>
         </is>
       </c>
       <c r="B353" s="5" t="n">
@@ -13227,7 +13227,7 @@
       <c r="F353" s="4" t="inlineStr"/>
       <c r="G353" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H353" s="4" t="n">
@@ -13235,19 +13235,19 @@
       </c>
       <c r="I353" s="4" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Maria Fernanda Medina Reyes; Juan Gabriel Fajardo Cuadro; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J353" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="354" ht="16" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105010266217</t>
+          <t>2-s2.0-105010313315</t>
         </is>
       </c>
       <c r="B354" s="3" t="n">
@@ -13263,7 +13263,7 @@
       <c r="F354" s="2" t="inlineStr"/>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H354" s="2" t="n">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes; Juan Gabriel Fajardo Cuadro; Juan Carlos Martinez Santos</t>
+          <t>Jose Luis Villa Ramirez; Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -13283,7 +13283,7 @@
     <row r="355" ht="16" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105010313315</t>
+          <t>2-s2.0-105010515590</t>
         </is>
       </c>
       <c r="B355" s="5" t="n">
@@ -13307,19 +13307,19 @@
       </c>
       <c r="I355" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Yady Tatiana Solano Correa</t>
+          <t>Stefania Arias Cifuentes; Iris Laudith Solano Cahuana</t>
         </is>
       </c>
       <c r="J355" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Centro de Idiomas</t>
         </is>
       </c>
     </row>
     <row r="356" ht="16" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105010515590</t>
+          <t>2-s2.0-105011497532</t>
         </is>
       </c>
       <c r="B356" s="3" t="n">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr"/>
@@ -13335,7 +13335,7 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H356" s="2" t="n">
@@ -13343,19 +13343,19 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>Stefania Arias Cifuentes; Iris Laudith Solano Cahuana</t>
+          <t>Vilma Viviana Ojeda Caicedo; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>Centro de Idiomas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="357" ht="16" customHeight="1">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105011497532</t>
+          <t>2-s2.0-105011838057</t>
         </is>
       </c>
       <c r="B357" s="5" t="n">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
       <c r="F357" s="4" t="inlineStr"/>
       <c r="G357" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H357" s="4" t="n">
@@ -13379,19 +13379,19 @@
       </c>
       <c r="I357" s="4" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Sonia Helena Contreras Ortiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J357" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="358" ht="16" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105011838057</t>
+          <t>2-s2.0-105012372534</t>
         </is>
       </c>
       <c r="B358" s="3" t="n">
@@ -13407,7 +13407,7 @@
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H358" s="2" t="n">
@@ -13415,19 +13415,19 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Lien Neil Tejeda López</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="359" ht="16" customHeight="1">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105012372534</t>
+          <t>2-s2.0-105012767262</t>
         </is>
       </c>
       <c r="B359" s="5" t="n">
@@ -13443,7 +13443,7 @@
       <c r="F359" s="4" t="inlineStr"/>
       <c r="G359" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H359" s="4" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="I359" s="4" t="inlineStr">
         <is>
-          <t>Lien Neil Tejeda López</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J359" s="4" t="inlineStr">
@@ -13463,7 +13463,7 @@
     <row r="360" ht="16" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105012767262</t>
+          <t>2-s2.0-105012947038</t>
         </is>
       </c>
       <c r="B360" s="3" t="n">
@@ -13479,7 +13479,7 @@
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H360" s="2" t="n">
@@ -13487,19 +13487,19 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Jenifer Yoris Vasquez Aguilar; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="361" ht="16" customHeight="1">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105012947038</t>
+          <t>2-s2.0-105013839047</t>
         </is>
       </c>
       <c r="B361" s="5" t="n">
@@ -13515,7 +13515,7 @@
       <c r="F361" s="4" t="inlineStr"/>
       <c r="G361" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H361" s="4" t="n">
@@ -13523,19 +13523,19 @@
       </c>
       <c r="I361" s="4" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Francisco Useche Vivero</t>
         </is>
       </c>
       <c r="J361" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="362" ht="16" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105013839047</t>
+          <t>2-s2.0-105014428683</t>
         </is>
       </c>
       <c r="B362" s="3" t="n">
@@ -13551,7 +13551,7 @@
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H362" s="2" t="n">
@@ -13559,19 +13559,19 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>Jairo Francisco Useche Vivero</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="363" ht="16" customHeight="1">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105014428683</t>
+          <t>2-s2.0-105014601429</t>
         </is>
       </c>
       <c r="B363" s="5" t="n">
@@ -13587,7 +13587,7 @@
       <c r="F363" s="4" t="inlineStr"/>
       <c r="G363" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H363" s="4" t="n">
@@ -13595,19 +13595,19 @@
       </c>
       <c r="I363" s="4" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Raul Andres Vargas Ramirez; Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
       <c r="J363" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="364" ht="16" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105014601429</t>
+          <t>2-s2.0-105014804906</t>
         </is>
       </c>
       <c r="B364" s="3" t="n">
@@ -13623,7 +13623,7 @@
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H364" s="2" t="n">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Andres Guillermo Marrugo Hernandez</t>
+          <t>Argemiro Palencia Diaz</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
@@ -13643,7 +13643,7 @@
     <row r="365" ht="16" customHeight="1">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105014804906</t>
+          <t>2-s2.0-105015050458</t>
         </is>
       </c>
       <c r="B365" s="5" t="n">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr"/>
@@ -13667,19 +13667,19 @@
       </c>
       <c r="I365" s="4" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J365" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="366" ht="16" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105015050458</t>
+          <t>2-s2.0-105015214420</t>
         </is>
       </c>
       <c r="B366" s="3" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr"/>
@@ -13695,7 +13695,7 @@
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H366" s="2" t="n">
@@ -13703,19 +13703,19 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Karol Patricia Gutierrez Ruiz; William Arellano Cartagena</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="367" ht="16" customHeight="1">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105015214420</t>
+          <t>2-s2.0-105015372289</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
@@ -13731,7 +13731,7 @@
       <c r="F367" s="4" t="inlineStr"/>
       <c r="G367" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H367" s="4" t="n">
@@ -13739,19 +13739,19 @@
       </c>
       <c r="I367" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz; William Arellano Cartagena</t>
+          <t>Jairo Francisco Useche Vivero</t>
         </is>
       </c>
       <c r="J367" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="368" ht="16" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105015372289</t>
+          <t>2-s2.0-105015383849</t>
         </is>
       </c>
       <c r="B368" s="3" t="n">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>Jairo Francisco Useche Vivero</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
     <row r="369" ht="16" customHeight="1">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105015383849</t>
+          <t>2-s2.0-105015723252</t>
         </is>
       </c>
       <c r="B369" s="5" t="n">
@@ -13803,7 +13803,7 @@
       <c r="F369" s="4" t="inlineStr"/>
       <c r="G369" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H369" s="4" t="n">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="I369" s="4" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="J369" s="4" t="inlineStr">
@@ -13823,7 +13823,7 @@
     <row r="370" ht="16" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105015723252</t>
+          <t>2-s2.0-105016331457</t>
         </is>
       </c>
       <c r="B370" s="3" t="n">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr"/>
@@ -13839,7 +13839,7 @@
       <c r="F370" s="2" t="inlineStr"/>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H370" s="2" t="n">
@@ -13847,19 +13847,19 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Maria Fernanda Medina Reyes; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="371" ht="16" customHeight="1">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105016331457</t>
+          <t>2-s2.0-105016793869</t>
         </is>
       </c>
       <c r="B371" s="5" t="n">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr"/>
@@ -13875,7 +13875,7 @@
       <c r="F371" s="4" t="inlineStr"/>
       <c r="G371" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H371" s="4" t="n">
@@ -13883,19 +13883,19 @@
       </c>
       <c r="I371" s="4" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="J371" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="372" ht="16" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105016793869</t>
+          <t>2-s2.0-105017060801</t>
         </is>
       </c>
       <c r="B372" s="3" t="n">
@@ -13911,7 +13911,7 @@
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H372" s="2" t="n">
@@ -13919,19 +13919,19 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Alberto Patiño Vanegas; Carlos Rafael Payares Guevara; Enrique Pereira Batista</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="373" ht="16" customHeight="1">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105017060801</t>
+          <t>2-s2.0-105017120204</t>
         </is>
       </c>
       <c r="B373" s="5" t="n">
@@ -13947,7 +13947,7 @@
       <c r="F373" s="4" t="inlineStr"/>
       <c r="G373" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H373" s="4" t="n">
@@ -13955,19 +13955,19 @@
       </c>
       <c r="I373" s="4" t="inlineStr">
         <is>
-          <t>Alberto Patiño Vanegas; Carlos Rafael Payares Guevara; Enrique Pereira Batista</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J373" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="374" ht="16" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105017120204</t>
+          <t>2-s2.0-105017596171</t>
         </is>
       </c>
       <c r="B374" s="3" t="n">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr"/>
@@ -13983,7 +13983,7 @@
       <c r="F374" s="2" t="inlineStr"/>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H374" s="2" t="n">
@@ -13991,19 +13991,19 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Andres Guillermo Marrugo Hernandez; Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="375" ht="16" customHeight="1">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105017596171</t>
+          <t>2-s2.0-105017713410</t>
         </is>
       </c>
       <c r="B375" s="5" t="n">
@@ -14027,19 +14027,19 @@
       </c>
       <c r="I375" s="4" t="inlineStr">
         <is>
-          <t>Andres Guillermo Marrugo Hernandez; Yady Tatiana Solano Correa</t>
+          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
       <c r="J375" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="376" ht="16" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105017713410</t>
+          <t>2-s2.0-105018752230</t>
         </is>
       </c>
       <c r="B376" s="3" t="n">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr"/>
@@ -14055,7 +14055,7 @@
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H376" s="2" t="n">
@@ -14063,19 +14063,19 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Andres Guillermo Marrugo Hernandez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="377" ht="16" customHeight="1">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105018752230</t>
+          <t>2-s2.0-105018948069</t>
         </is>
       </c>
       <c r="B377" s="5" t="n">
@@ -14091,7 +14091,7 @@
       <c r="F377" s="4" t="inlineStr"/>
       <c r="G377" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H377" s="4" t="n">
@@ -14099,19 +14099,19 @@
       </c>
       <c r="I377" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="J377" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="378" ht="16" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105018948069</t>
+          <t>2-s2.0-105019042517</t>
         </is>
       </c>
       <c r="B378" s="3" t="n">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr"/>
@@ -14127,7 +14127,7 @@
       <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H378" s="2" t="n">
@@ -14135,19 +14135,19 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Jairo Enrique Serrano Castañeda; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="379" ht="16" customHeight="1">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019042517</t>
+          <t>2-s2.0-105019042653</t>
         </is>
       </c>
       <c r="B379" s="5" t="n">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="I379" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Edwin Alexander Puertas del Castillo; Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J379" s="4" t="inlineStr">
@@ -14183,7 +14183,7 @@
     <row r="380" ht="16" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019042653</t>
+          <t>2-s2.0-105019045699</t>
         </is>
       </c>
       <c r="B380" s="3" t="n">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
     <row r="381" ht="16" customHeight="1">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019045699</t>
+          <t>2-s2.0-105019046953</t>
         </is>
       </c>
       <c r="B381" s="5" t="n">
@@ -14255,7 +14255,7 @@
     <row r="382" ht="16" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019046953</t>
+          <t>2-s2.0-105019047967</t>
         </is>
       </c>
       <c r="B382" s="3" t="n">
@@ -14291,7 +14291,7 @@
     <row r="383" ht="16" customHeight="1">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019047967</t>
+          <t>2-s2.0-105019055348</t>
         </is>
       </c>
       <c r="B383" s="5" t="n">
@@ -14327,7 +14327,7 @@
     <row r="384" ht="16" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019055348</t>
+          <t>2-s2.0-105019057081</t>
         </is>
       </c>
       <c r="B384" s="3" t="n">
@@ -14363,7 +14363,7 @@
     <row r="385" ht="16" customHeight="1">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019057081</t>
+          <t>2-s2.0-105019057106</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="I385" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J385" s="4" t="inlineStr">
@@ -14399,7 +14399,7 @@
     <row r="386" ht="16" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019057106</t>
+          <t>2-s2.0-105019059160</t>
         </is>
       </c>
       <c r="B386" s="3" t="n">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -14435,7 +14435,7 @@
     <row r="387" ht="16" customHeight="1">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019059160</t>
+          <t>2-s2.0-105019059289</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="I387" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda; Edwin Alexander Puertas del Castillo</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J387" s="4" t="inlineStr">
@@ -14471,7 +14471,7 @@
     <row r="388" ht="16" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019059289</t>
+          <t>2-s2.0-105019059818</t>
         </is>
       </c>
       <c r="B388" s="3" t="n">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
@@ -14507,7 +14507,7 @@
     <row r="389" ht="16" customHeight="1">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019059818</t>
+          <t>2-s2.0-105019060674</t>
         </is>
       </c>
       <c r="B389" s="5" t="n">
@@ -14543,7 +14543,7 @@
     <row r="390" ht="16" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019060674</t>
+          <t>2-s2.0-105019228134</t>
         </is>
       </c>
       <c r="B390" s="3" t="n">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr"/>
@@ -14567,19 +14567,19 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jairo Francisco Useche Vivero</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="391" ht="16" customHeight="1">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019228134</t>
+          <t>2-s2.0-105019292532</t>
         </is>
       </c>
       <c r="B391" s="5" t="n">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="I391" s="4" t="inlineStr">
         <is>
-          <t>Jairo Francisco Useche Vivero</t>
+          <t>Harold Alberto Rodriguez Arias</t>
         </is>
       </c>
       <c r="J391" s="4" t="inlineStr">
@@ -14615,7 +14615,7 @@
     <row r="392" ht="16" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019292532</t>
+          <t>2-s2.0-105019292877</t>
         </is>
       </c>
       <c r="B392" s="3" t="n">
@@ -14639,19 +14639,19 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>Harold Alberto Rodriguez Arias</t>
+          <t>Jorge Luis Villalba Acevedo; Alberto Patiño Vanegas; Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="393" ht="16" customHeight="1">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019292877</t>
+          <t>2-s2.0-105019294032</t>
         </is>
       </c>
       <c r="B393" s="5" t="n">
@@ -14675,19 +14675,19 @@
       </c>
       <c r="I393" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis Villalba Acevedo; Alberto Patiño Vanegas; Edisson Chavarro Mesa</t>
+          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino; Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J393" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="394" ht="16" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019294032</t>
+          <t>2-s2.0-105019296053</t>
         </is>
       </c>
       <c r="B394" s="3" t="n">
@@ -14711,19 +14711,19 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino; Rosa Leonor Acevedo Barrios</t>
+          <t>Carlos Rafael Payares Guevara; Enrique Pereira Batista; Hernando Rafael Altamar Mercado; Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="395" ht="16" customHeight="1">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019296053</t>
+          <t>2-s2.0-105019296951</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
@@ -14747,19 +14747,19 @@
       </c>
       <c r="I395" s="4" t="inlineStr">
         <is>
-          <t>Carlos Rafael Payares Guevara; Enrique Pereira Batista; Hernando Rafael Altamar Mercado; Alberto Patiño Vanegas</t>
+          <t>Sonia Helena Contreras Ortiz; Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="396" ht="16" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019296951</t>
+          <t>2-s2.0-105019297942</t>
         </is>
       </c>
       <c r="B396" s="3" t="n">
@@ -14783,19 +14783,19 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz; Vilma Viviana Ojeda Caicedo; Hernando Rafael Altamar Mercado; Juan Carlos Martinez Santos</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="397" ht="16" customHeight="1">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019297942</t>
+          <t>2-s2.0-105019298893</t>
         </is>
       </c>
       <c r="B397" s="5" t="n">
@@ -14819,19 +14819,19 @@
       </c>
       <c r="I397" s="4" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo</t>
+          <t>Jorgelina Cecilia Pasqualino; Diana Carolina Rubiano Labrador; Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="J397" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="398" ht="16" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019298893</t>
+          <t>2-s2.0-105019299654</t>
         </is>
       </c>
       <c r="B398" s="3" t="n">
@@ -14855,19 +14855,19 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>Jorgelina Cecilia Pasqualino; Diana Carolina Rubiano Labrador; Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Edisson Chavarro Mesa</t>
+          <t>Alba Zulay Cardenas Escobar; Armando Antonio Mendoza Diaz; Holman Ospina Mateus</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="399" ht="16" customHeight="1">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019299654</t>
+          <t>2-s2.0-105019304186</t>
         </is>
       </c>
       <c r="B399" s="5" t="n">
@@ -14891,19 +14891,19 @@
       </c>
       <c r="I399" s="4" t="inlineStr">
         <is>
-          <t>Alba Zulay Cardenas Escobar; Armando Antonio Mendoza Diaz; Holman Ospina Mateus</t>
+          <t>Alba Zulay Cardenas Escobar; Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="J399" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="400" ht="16" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019304186</t>
+          <t>2-s2.0-105019305725</t>
         </is>
       </c>
       <c r="B400" s="3" t="n">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>Alba Zulay Cardenas Escobar; Lina Margarita Marrugo Salas</t>
+          <t>Veronica Tordecilla Acevedo</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr">
@@ -14939,7 +14939,7 @@
     <row r="401" ht="16" customHeight="1">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019305725</t>
+          <t>2-s2.0-105019307782</t>
         </is>
       </c>
       <c r="B401" s="5" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="I401" s="4" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo</t>
+          <t>Veronica Tordecilla Acevedo; Juan Camilo Medellin Rojas; Alba Zulay Cardenas Escobar</t>
         </is>
       </c>
       <c r="J401" s="4" t="inlineStr">
@@ -14975,7 +14975,7 @@
     <row r="402" ht="16" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019307782</t>
+          <t>2-s2.0-105019308753</t>
         </is>
       </c>
       <c r="B402" s="3" t="n">
@@ -14999,19 +14999,19 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>Veronica Tordecilla Acevedo; Juan Camilo Medellin Rojas; Alba Zulay Cardenas Escobar</t>
+          <t>Harold Alberto Rodriguez Arias</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="403" ht="16" customHeight="1">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019308753</t>
+          <t>2-s2.0-105019311488</t>
         </is>
       </c>
       <c r="B403" s="5" t="n">
@@ -15035,19 +15035,19 @@
       </c>
       <c r="I403" s="4" t="inlineStr">
         <is>
-          <t>Harold Alberto Rodriguez Arias</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador; Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="404" ht="16" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019311488</t>
+          <t>2-s2.0-105019312007</t>
         </is>
       </c>
       <c r="B404" s="3" t="n">
@@ -15071,19 +15071,19 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador; Jorge Luis Villalba Acevedo</t>
+          <t>Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="405" ht="16" customHeight="1">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019312007</t>
+          <t>2-s2.0-105019313383</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
@@ -15107,19 +15107,19 @@
       </c>
       <c r="I405" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina; Alba Zulay Cardenas Escobar; Oriana Susana Martinez Palomino</t>
+          <t>Sonia Helena Contreras Ortiz; Vilma Viviana Ojeda Caicedo; Juan Carlos Martinez Santos; Danilo Lusbin Ariza Rua</t>
         </is>
       </c>
       <c r="J405" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="406" ht="16" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019313383</t>
+          <t>2-s2.0-105019313699</t>
         </is>
       </c>
       <c r="B406" s="3" t="n">
@@ -15143,19 +15143,19 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz; Vilma Viviana Ojeda Caicedo; Juan Carlos Martinez Santos; Danilo Lusbin Ariza Rua</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="407" ht="16" customHeight="1">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019313699</t>
+          <t>2-s2.0-105019314605</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
@@ -15179,19 +15179,19 @@
       </c>
       <c r="I407" s="4" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="J407" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="408" ht="16" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019314605</t>
+          <t>2-s2.0-105019315684</t>
         </is>
       </c>
       <c r="B408" s="3" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>Hernando Rafael Altamar Mercado; Carlos Rafael Payares Guevara; Enrique Pereira Batista; Vilma Viviana Ojeda Caicedo; Alberto Patiño Vanegas</t>
+          <t>Diana Carolina Rubiano Labrador; Danilo Lusbin Ariza Rua</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -15227,7 +15227,7 @@
     <row r="409" ht="16" customHeight="1">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019315684</t>
+          <t>2-s2.0-105019318293</t>
         </is>
       </c>
       <c r="B409" s="5" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="I409" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador; Danilo Lusbin Ariza Rua</t>
+          <t>Diana Carolina Rubiano Labrador; Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="J409" s="4" t="inlineStr">
@@ -15263,7 +15263,7 @@
     <row r="410" ht="16" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019318293</t>
+          <t>2-s2.0-105019318561</t>
         </is>
       </c>
       <c r="B410" s="3" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador; Edisson Chavarro Mesa</t>
+          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -15299,7 +15299,7 @@
     <row r="411" ht="16" customHeight="1">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019318561</t>
+          <t>2-s2.0-105019318823</t>
         </is>
       </c>
       <c r="B411" s="5" t="n">
@@ -15323,19 +15323,19 @@
       </c>
       <c r="I411" s="4" t="inlineStr">
         <is>
-          <t>Danilo Lusbin Ariza Rua; Alberto Patiño Vanegas; Vilma Viviana Ojeda Caicedo; Jorge Luis Villalba Acevedo</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J411" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="412" ht="16" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019318823</t>
+          <t>2-s2.0-105019319114</t>
         </is>
       </c>
       <c r="B412" s="3" t="n">
@@ -15359,19 +15359,19 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Jorgelina Cecilia Pasqualino; Claudia Patricia Diaz Mendoza; Edisson Chavarro Mesa; Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="413" ht="16" customHeight="1">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019319114</t>
+          <t>2-s2.0-105019319476</t>
         </is>
       </c>
       <c r="B413" s="5" t="n">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="I413" s="4" t="inlineStr">
         <is>
-          <t>Jorgelina Cecilia Pasqualino; Claudia Patricia Diaz Mendoza; Edisson Chavarro Mesa; Rosa Leonor Acevedo Barrios</t>
+          <t>Jorgelina Cecilia Pasqualino; Claudia Patricia Diaz Mendoza; Diana Carolina Rubiano Labrador; Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J413" s="4" t="inlineStr">
@@ -15407,7 +15407,7 @@
     <row r="414" ht="16" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019319476</t>
+          <t>2-s2.0-105019322610</t>
         </is>
       </c>
       <c r="B414" s="3" t="n">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>Jorgelina Cecilia Pasqualino; Claudia Patricia Diaz Mendoza; Diana Carolina Rubiano Labrador; Rosa Leonor Acevedo Barrios</t>
+          <t>Rosa Leonor Acevedo Barrios; Jorgelina Cecilia Pasqualino</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -15443,7 +15443,7 @@
     <row r="415" ht="16" customHeight="1">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019322610</t>
+          <t>2-s2.0-105019375814</t>
         </is>
       </c>
       <c r="B415" s="5" t="n">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="C415" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr"/>
@@ -15459,7 +15459,7 @@
       <c r="F415" s="4" t="inlineStr"/>
       <c r="G415" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H415" s="4" t="n">
@@ -15467,19 +15467,19 @@
       </c>
       <c r="I415" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Jorgelina Cecilia Pasqualino</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="J415" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="416" ht="16" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019375814</t>
+          <t>2-s2.0-105019965329</t>
         </is>
       </c>
       <c r="B416" s="3" t="n">
@@ -15495,7 +15495,7 @@
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H416" s="2" t="n">
@@ -15503,19 +15503,19 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="417" ht="16" customHeight="1">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105019965329</t>
+          <t>2-s2.0-105019980686</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="C417" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr"/>
@@ -15531,7 +15531,7 @@
       <c r="F417" s="4" t="inlineStr"/>
       <c r="G417" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H417" s="4" t="n">
@@ -15539,19 +15539,19 @@
       </c>
       <c r="I417" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Cesar Augusto Viloria Nuñez; Tania Lucia Cobos Cobos; Isaac Zuñiga Silgado</t>
         </is>
       </c>
       <c r="J417" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="418" ht="16" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105019980686</t>
+          <t>2-s2.0-105020699906</t>
         </is>
       </c>
       <c r="B418" s="3" t="n">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr"/>
@@ -15567,7 +15567,7 @@
       <c r="F418" s="2" t="inlineStr"/>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H418" s="2" t="n">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez; Tania Lucia Cobos Cobos; Isaac Zuñiga Silgado</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
     <row r="419" ht="16" customHeight="1">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020699906</t>
+          <t>2-s2.0-105020957466</t>
         </is>
       </c>
       <c r="B419" s="5" t="n">
@@ -15603,7 +15603,7 @@
       <c r="F419" s="4" t="inlineStr"/>
       <c r="G419" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H419" s="4" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="I419" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J419" s="4" t="inlineStr">
@@ -15623,7 +15623,7 @@
     <row r="420" ht="16" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020957466</t>
+          <t>2-s2.0-105021498401</t>
         </is>
       </c>
       <c r="B420" s="3" t="n">
@@ -15639,7 +15639,7 @@
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H420" s="2" t="n">
@@ -15647,19 +15647,19 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Alfredo Miguel Abuchar Curi; Argemiro Palencia Diaz</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="421" ht="16" customHeight="1">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105021498401</t>
+          <t>2-s2.0-105021543213</t>
         </is>
       </c>
       <c r="B421" s="5" t="n">
@@ -15675,7 +15675,7 @@
       <c r="F421" s="4" t="inlineStr"/>
       <c r="G421" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H421" s="4" t="n">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="I421" s="4" t="inlineStr">
         <is>
-          <t>Alfredo Miguel Abuchar Curi; Argemiro Palencia Diaz</t>
+          <t>Jorgelina Cecilia Pasqualino</t>
         </is>
       </c>
       <c r="J421" s="4" t="inlineStr">
@@ -15695,7 +15695,7 @@
     <row r="422" ht="16" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105021543213</t>
+          <t>2-s2.0-105021565579</t>
         </is>
       </c>
       <c r="B422" s="3" t="n">
@@ -15711,7 +15711,7 @@
       <c r="F422" s="2" t="inlineStr"/>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H422" s="2" t="n">
@@ -15719,19 +15719,19 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>Jorgelina Cecilia Pasqualino</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="423" ht="16" customHeight="1">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105021565579</t>
+          <t>2-s2.0-105021810439</t>
         </is>
       </c>
       <c r="B423" s="5" t="n">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="C423" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr"/>
@@ -15755,19 +15755,19 @@
       </c>
       <c r="I423" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J423" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="424" ht="16" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105021810439</t>
+          <t>2-s2.0-105022088435</t>
         </is>
       </c>
       <c r="B424" s="3" t="n">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr"/>
@@ -15783,7 +15783,7 @@
       <c r="F424" s="2" t="inlineStr"/>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H424" s="2" t="n">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -15803,7 +15803,7 @@
     <row r="425" ht="16" customHeight="1">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105022088435</t>
+          <t>2-s2.0-105023066099</t>
         </is>
       </c>
       <c r="B425" s="5" t="n">
@@ -15819,7 +15819,7 @@
       <c r="F425" s="4" t="inlineStr"/>
       <c r="G425" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H425" s="4" t="n">
@@ -15827,19 +15827,19 @@
       </c>
       <c r="I425" s="4" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J425" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="426" ht="16" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105023066099</t>
+          <t>2-s2.0-105023171457</t>
         </is>
       </c>
       <c r="B426" s="3" t="n">
@@ -15855,7 +15855,7 @@
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H426" s="2" t="n">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr">
@@ -15875,7 +15875,7 @@
     <row r="427" ht="16" customHeight="1">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105023171457</t>
+          <t>2-s2.0-105023499318</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
@@ -15891,7 +15891,7 @@
       <c r="F427" s="4" t="inlineStr"/>
       <c r="G427" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H427" s="4" t="n">
@@ -15899,19 +15899,19 @@
       </c>
       <c r="I427" s="4" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Pedro Vazquez Miraz; Graciela Victoria Franco Martinez</t>
         </is>
       </c>
       <c r="J427" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Dirección de Humanidades; Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="428" ht="16" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105023499318</t>
+          <t>2-s2.0-105024556972</t>
         </is>
       </c>
       <c r="B428" s="3" t="n">
@@ -15927,7 +15927,7 @@
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H428" s="2" t="n">
@@ -15935,19 +15935,19 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz; Graciela Victoria Franco Martinez</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>Dirección de Humanidades; Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="429" ht="16" customHeight="1">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105024556972</t>
+          <t>2-s2.0-105024594126</t>
         </is>
       </c>
       <c r="B429" s="5" t="n">
@@ -15963,7 +15963,7 @@
       <c r="F429" s="4" t="inlineStr"/>
       <c r="G429" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H429" s="4" t="n">
@@ -15971,19 +15971,19 @@
       </c>
       <c r="I429" s="4" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="J429" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="430" ht="16" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105024594126</t>
+          <t>2-s2.0-105025551761</t>
         </is>
       </c>
       <c r="B430" s="3" t="n">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr"/>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="431" ht="16" customHeight="1">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105025551761</t>
+          <t>2-s2.0-105028745753</t>
         </is>
       </c>
       <c r="B431" s="5" t="n">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="C431" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr"/>
@@ -16035,7 +16035,7 @@
       <c r="F431" s="4" t="inlineStr"/>
       <c r="G431" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H431" s="4" t="n">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="I431" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Argemiro Palencia Diaz</t>
         </is>
       </c>
       <c r="J431" s="4" t="inlineStr">
@@ -16055,7 +16055,7 @@
     <row r="432" ht="16" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028745753</t>
+          <t>2-s2.0-105028746459</t>
         </is>
       </c>
       <c r="B432" s="3" t="n">
@@ -16091,7 +16091,7 @@
     <row r="433" ht="16" customHeight="1">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028746459</t>
+          <t>2-s2.0-105029095582</t>
         </is>
       </c>
       <c r="B433" s="5" t="n">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="I433" s="4" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz</t>
+          <t>Jairo Francisco Useche Vivero</t>
         </is>
       </c>
       <c r="J433" s="4" t="inlineStr">
@@ -16127,7 +16127,7 @@
     <row r="434" ht="16" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029095582</t>
+          <t>2-s2.0-105029608036</t>
         </is>
       </c>
       <c r="B434" s="3" t="n">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr"/>
@@ -16143,7 +16143,7 @@
       <c r="F434" s="2" t="inlineStr"/>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H434" s="2" t="n">
@@ -16151,19 +16151,19 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>Jairo Francisco Useche Vivero</t>
+          <t>James Manuel Perez Moron; Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="435" ht="16" customHeight="1">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029608036</t>
+          <t>2-s2.0-105029608377</t>
         </is>
       </c>
       <c r="B435" s="5" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="I435" s="4" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron; Lina Margarita Marrugo Salas</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J435" s="4" t="inlineStr">
@@ -16199,7 +16199,7 @@
     <row r="436" ht="16" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029608377</t>
+          <t>2-s2.0-105029610624</t>
         </is>
       </c>
       <c r="B436" s="3" t="n">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Lina Margarita Marrugo Salas; James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -16235,7 +16235,7 @@
     <row r="437" ht="16" customHeight="1">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029610624</t>
+          <t>2-s2.0-105029790270</t>
         </is>
       </c>
       <c r="B437" s="5" t="n">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="C437" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr"/>
@@ -16259,19 +16259,19 @@
       </c>
       <c r="I437" s="4" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas; James Manuel Perez Moron</t>
+          <t>Yuranis Henriquez Nuñez; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J437" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="438" ht="16" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029790270</t>
+          <t>2-s2.0-105029800450</t>
         </is>
       </c>
       <c r="B438" s="3" t="n">
@@ -16295,19 +16295,19 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez; Jairo Enrique Serrano Castañeda</t>
+          <t>Jorge Luis del Rio Cortina; Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="439" ht="16" customHeight="1">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029800450</t>
+          <t>2-s2.0-105029801421</t>
         </is>
       </c>
       <c r="B439" s="5" t="n">
@@ -16331,19 +16331,19 @@
       </c>
       <c r="I439" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina; Rita Cecilia de la Hoz del Villar</t>
+          <t>Argemiro Palencia Diaz</t>
         </is>
       </c>
       <c r="J439" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="440" ht="16" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029801421</t>
+          <t>2-s2.0-105029801788</t>
         </is>
       </c>
       <c r="B440" s="3" t="n">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -16379,7 +16379,7 @@
     <row r="441" ht="16" customHeight="1">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029801788</t>
+          <t>2-s2.0-105029802872</t>
         </is>
       </c>
       <c r="B441" s="5" t="n">
@@ -16403,19 +16403,19 @@
       </c>
       <c r="I441" s="4" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J441" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="442" ht="16" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029802872</t>
+          <t>2-s2.0-105029805214</t>
         </is>
       </c>
       <c r="B442" s="3" t="n">
@@ -16439,19 +16439,19 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="443" ht="16" customHeight="1">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029805214</t>
+          <t>2-s2.0-105029817748</t>
         </is>
       </c>
       <c r="B443" s="5" t="n">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="I443" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Oscar Acevedo Patiño</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J443" s="4" t="inlineStr">
@@ -16487,7 +16487,7 @@
     <row r="444" ht="16" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029817748</t>
+          <t>2-s2.0-105029849389</t>
         </is>
       </c>
       <c r="B444" s="3" t="n">
@@ -16511,19 +16511,19 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="445" ht="16" customHeight="1">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029849389</t>
+          <t>2-s2.0-105029858305</t>
         </is>
       </c>
       <c r="B445" s="5" t="n">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I445" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J445" s="4" t="inlineStr">
@@ -16559,7 +16559,7 @@
     <row r="446" ht="16" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029858305</t>
+          <t>2-s2.0-105029874426</t>
         </is>
       </c>
       <c r="B446" s="3" t="n">
@@ -16595,7 +16595,7 @@
     <row r="447" ht="16" customHeight="1">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029874426</t>
+          <t>2-s2.0-105029882159</t>
         </is>
       </c>
       <c r="B447" s="5" t="n">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="I447" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Yuranis Henriquez Nuñez; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J447" s="4" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="448" ht="16" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029882159</t>
+          <t>2-s2.0-105029882771</t>
         </is>
       </c>
       <c r="B448" s="3" t="n">
@@ -16655,19 +16655,19 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="449" ht="16" customHeight="1">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029882771</t>
+          <t>2-s2.0-105029883235</t>
         </is>
       </c>
       <c r="B449" s="5" t="n">
@@ -16691,19 +16691,19 @@
       </c>
       <c r="I449" s="4" t="inlineStr">
         <is>
-          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J449" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="450" ht="16" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029883235</t>
+          <t>2-s2.0-105029886547</t>
         </is>
       </c>
       <c r="B450" s="3" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -16739,7 +16739,7 @@
     <row r="451" ht="16" customHeight="1">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029886547</t>
+          <t>2-s2.0-105030540249</t>
         </is>
       </c>
       <c r="B451" s="5" t="n">
@@ -16763,19 +16763,19 @@
       </c>
       <c r="I451" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Lina Margarita Marrugo Salas; Alba Zulay Cardenas Escobar</t>
         </is>
       </c>
       <c r="J451" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="452" ht="16" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105030540249</t>
+          <t>2-s2.0-105031353281</t>
         </is>
       </c>
       <c r="B452" s="3" t="n">
@@ -16799,19 +16799,19 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas; Alba Zulay Cardenas Escobar</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="453" ht="16" customHeight="1">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031353281</t>
+          <t>2-s2.0-105031377830</t>
         </is>
       </c>
       <c r="B453" s="5" t="n">
@@ -16847,7 +16847,7 @@
     <row r="454" ht="16" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031377830</t>
+          <t>2-s2.0-105031405066</t>
         </is>
       </c>
       <c r="B454" s="3" t="n">
@@ -16871,19 +16871,19 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Holman Ospina Mateus</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="455" ht="16" customHeight="1">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031405066</t>
+          <t>2-s2.0-105031438328</t>
         </is>
       </c>
       <c r="B455" s="5" t="n">
@@ -16907,19 +16907,19 @@
       </c>
       <c r="I455" s="4" t="inlineStr">
         <is>
-          <t>Holman Ospina Mateus</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J455" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="456" ht="16" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031438328</t>
+          <t>2-s2.0-105031646619</t>
         </is>
       </c>
       <c r="B456" s="3" t="n">
@@ -16955,7 +16955,7 @@
     <row r="457" ht="16" customHeight="1">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031646619</t>
+          <t>2-s2.0-105032391934</t>
         </is>
       </c>
       <c r="B457" s="5" t="n">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="I457" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Yuranis Henriquez Nuñez; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J457" s="4" t="inlineStr">
@@ -16991,7 +16991,7 @@
     <row r="458" ht="16" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105032391934</t>
+          <t>2-s2.0-105032413655</t>
         </is>
       </c>
       <c r="B458" s="3" t="n">
@@ -17015,19 +17015,19 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>Yuranis Henriquez Nuñez; Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Vilma Viviana Ojeda Caicedo; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="459" ht="16" customHeight="1">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105032413655</t>
+          <t>2-s2.0-105032465061</t>
         </is>
       </c>
       <c r="B459" s="5" t="n">
@@ -17063,7 +17063,7 @@
     <row r="460" ht="16" customHeight="1">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105032465061</t>
+          <t>2-s2.0-105032487228</t>
         </is>
       </c>
       <c r="B460" s="3" t="n">
@@ -17087,19 +17087,19 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo; Sonia Helena Contreras Ortiz</t>
+          <t>Alba Zulay Cardenas Escobar; Armando Antonio Mendoza Diaz</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="461" ht="16" customHeight="1">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105032487228</t>
+          <t>2-s2.0-105032496247</t>
         </is>
       </c>
       <c r="B461" s="5" t="n">
@@ -17123,19 +17123,19 @@
       </c>
       <c r="I461" s="4" t="inlineStr">
         <is>
-          <t>Alba Zulay Cardenas Escobar; Armando Antonio Mendoza Diaz</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J461" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="462" ht="16" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105032496247</t>
+          <t>2-s2.0-105032508414</t>
         </is>
       </c>
       <c r="B462" s="3" t="n">
@@ -17159,19 +17159,19 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="463" ht="16" customHeight="1">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105032508414</t>
+          <t>2-s2.0-105032536852</t>
         </is>
       </c>
       <c r="B463" s="5" t="n">
@@ -17195,19 +17195,19 @@
       </c>
       <c r="I463" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J463" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="464" ht="16" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105032536852</t>
+          <t>2-s2.0-105033108892</t>
         </is>
       </c>
       <c r="B464" s="3" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr"/>
@@ -17223,7 +17223,7 @@
       <c r="F464" s="2" t="inlineStr"/>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H464" s="2" t="n">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -17243,7 +17243,7 @@
     <row r="465" ht="16" customHeight="1">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033108892</t>
+          <t>2-s2.0-105033316088</t>
         </is>
       </c>
       <c r="B465" s="5" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="C465" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr"/>
@@ -17259,7 +17259,7 @@
       <c r="F465" s="4" t="inlineStr"/>
       <c r="G465" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H465" s="4" t="n">
@@ -17267,19 +17267,19 @@
       </c>
       <c r="I465" s="4" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J465" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="466" ht="16" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033316088</t>
+          <t>2-s2.0-105033322669</t>
         </is>
       </c>
       <c r="B466" s="3" t="n">
@@ -17303,19 +17303,19 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo; Jairo Enrique Serrano Castañeda</t>
+          <t>Mauro Antonio Gonzalez Sierra; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="467" ht="16" customHeight="1">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033322669</t>
+          <t>2-s2.0-105033330778</t>
         </is>
       </c>
       <c r="B467" s="5" t="n">
@@ -17339,7 +17339,7 @@
       </c>
       <c r="I467" s="4" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra; Juan Carlos Martinez Santos</t>
+          <t>Jenifer Yoris Vasquez Aguilar; Edwin Alexander Puertas del Castillo; Armando Antonio Mendoza Diaz; Fabian Alfonso Gazabon Arrieta; Holman Ospina Mateus</t>
         </is>
       </c>
       <c r="J467" s="4" t="inlineStr">
@@ -17351,7 +17351,7 @@
     <row r="468" ht="16" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033330778</t>
+          <t>2-s2.0-105033330946</t>
         </is>
       </c>
       <c r="B468" s="3" t="n">
@@ -17375,19 +17375,19 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar; Edwin Alexander Puertas del Castillo; Armando Antonio Mendoza Diaz; Fabian Alfonso Gazabon Arrieta; Holman Ospina Mateus</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="469" ht="16" customHeight="1">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033330946</t>
+          <t>2-s2.0-105033331051</t>
         </is>
       </c>
       <c r="B469" s="5" t="n">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="I469" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Humberto Manuel Marbello Peña</t>
         </is>
       </c>
       <c r="J469" s="4" t="inlineStr">
@@ -17423,7 +17423,7 @@
     <row r="470" ht="16" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033331051</t>
+          <t>2-s2.0-105033331171</t>
         </is>
       </c>
       <c r="B470" s="3" t="n">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr">
@@ -17459,7 +17459,7 @@
     <row r="471" ht="16" customHeight="1">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033331171</t>
+          <t>2-s2.0-105033332264</t>
         </is>
       </c>
       <c r="B471" s="5" t="n">
@@ -17483,19 +17483,19 @@
       </c>
       <c r="I471" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Raul Andres Vargas Ramirez; Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
       <c r="J471" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="472" ht="16" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033332264</t>
+          <t>2-s2.0-105033332747</t>
         </is>
       </c>
       <c r="B472" s="3" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Andres Guillermo Marrugo Hernandez</t>
+          <t>Harold Alberto Rodriguez Arias</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -17531,7 +17531,7 @@
     <row r="473" ht="16" customHeight="1">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033332747</t>
+          <t>2-s2.0-105033333590</t>
         </is>
       </c>
       <c r="B473" s="5" t="n">
@@ -17555,19 +17555,19 @@
       </c>
       <c r="I473" s="4" t="inlineStr">
         <is>
-          <t>Harold Alberto Rodriguez Arias</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J473" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="474" ht="16" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033333590</t>
+          <t>2-s2.0-105033334115</t>
         </is>
       </c>
       <c r="B474" s="3" t="n">
@@ -17591,19 +17591,19 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Jorge Luis del Rio Cortina; Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="475" ht="16" customHeight="1">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033334115</t>
+          <t>2-s2.0-105033334472</t>
         </is>
       </c>
       <c r="B475" s="5" t="n">
@@ -17627,19 +17627,19 @@
       </c>
       <c r="I475" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina; Rita Cecilia de la Hoz del Villar</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="J475" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="476" ht="16" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033334472</t>
+          <t>2-s2.0-105033335211</t>
         </is>
       </c>
       <c r="B476" s="3" t="n">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -17675,7 +17675,7 @@
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033335211</t>
+          <t>2-s2.0-105033335561</t>
         </is>
       </c>
       <c r="B477" s="5" t="n">
@@ -17699,19 +17699,19 @@
       </c>
       <c r="I477" s="4" t="inlineStr">
         <is>
-          <t>Andres Guillermo Marrugo Hernandez</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J477" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="478" ht="16" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033335561</t>
+          <t>2-s2.0-105033335748</t>
         </is>
       </c>
       <c r="B478" s="3" t="n">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -17747,7 +17747,7 @@
     <row r="479" ht="16" customHeight="1">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033335748</t>
+          <t>2-s2.0-105033336016</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="I479" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
+          <t>Holman Ospina Mateus; Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="J479" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033336016</t>
+          <t>2-s2.0-105033337795</t>
         </is>
       </c>
       <c r="B480" s="3" t="n">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>Holman Ospina Mateus; Jenifer Yoris Vasquez Aguilar</t>
+          <t>Yina Paola Cabarcas Mena; Raul Andres Vargas Ramirez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -17819,7 +17819,7 @@
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033337795</t>
+          <t>2-s2.0-105033338017</t>
         </is>
       </c>
       <c r="B481" s="5" t="n">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="I481" s="4" t="inlineStr">
         <is>
-          <t>Yina Paola Cabarcas Mena; Raul Andres Vargas Ramirez; Sonia Helena Contreras Ortiz</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J481" s="4" t="inlineStr">
@@ -17855,7 +17855,7 @@
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033338017</t>
+          <t>2-s2.0-105033338867</t>
         </is>
       </c>
       <c r="B482" s="3" t="n">
@@ -17879,19 +17879,19 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033338867</t>
+          <t>2-s2.0-105033339414</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
@@ -17915,19 +17915,19 @@
       </c>
       <c r="I483" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J483" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033339414</t>
+          <t>2-s2.0-105033339428</t>
         </is>
       </c>
       <c r="B484" s="3" t="n">
@@ -17951,19 +17951,19 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033339428</t>
+          <t>2-s2.0-105033339488</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
@@ -17987,19 +17987,19 @@
       </c>
       <c r="I485" s="4" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Mauro Antonio Gonzalez Sierra; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J485" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033339488</t>
+          <t>2-s2.0-105033339541</t>
         </is>
       </c>
       <c r="B486" s="3" t="n">
@@ -18023,19 +18023,19 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra; Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033339541</t>
+          <t>2-s2.0-105033341328</t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="I487" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Jairo Enrique Serrano Castañeda</t>
+          <t>Julio Antonio Gomez Mora; Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J487" s="4" t="inlineStr">
@@ -18071,7 +18071,7 @@
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033341328</t>
+          <t>2-s2.0-105035998512</t>
         </is>
       </c>
       <c r="B488" s="3" t="n">
@@ -18095,19 +18095,19 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>Julio Antonio Gomez Mora; Cesar Augusto Viloria Nuñez</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035998512</t>
+          <t>2-s2.0-105036004446</t>
         </is>
       </c>
       <c r="B489" s="5" t="n">
@@ -18131,19 +18131,19 @@
       </c>
       <c r="I489" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Jairo Enrique Serrano Castañeda; Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J489" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105036004446</t>
+          <t>2-s2.0-105036004758</t>
         </is>
       </c>
       <c r="B490" s="3" t="n">
@@ -18167,19 +18167,19 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda; Yady Tatiana Solano Correa</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105036004758</t>
+          <t>2-s2.0-105036668257</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="C491" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr"/>
@@ -18195,7 +18195,7 @@
       <c r="F491" s="4" t="inlineStr"/>
       <c r="G491" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H491" s="4" t="n">
@@ -18203,19 +18203,19 @@
       </c>
       <c r="I491" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J491" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105036668257</t>
+          <t>2-s2.0-105036700784</t>
         </is>
       </c>
       <c r="B492" s="3" t="n">
@@ -18239,19 +18239,19 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105036700784</t>
+          <t>2-s2.0-105037107131</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="C493" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr"/>
@@ -18267,7 +18267,7 @@
       <c r="F493" s="4" t="inlineStr"/>
       <c r="G493" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H493" s="4" t="n">
@@ -18275,19 +18275,19 @@
       </c>
       <c r="I493" s="4" t="inlineStr">
         <is>
-          <t>Oscar Acevedo Patiño</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J493" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105037107131</t>
+          <t>2-s2.0-105037439775</t>
         </is>
       </c>
       <c r="B494" s="3" t="n">
@@ -18323,7 +18323,7 @@
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105037439775</t>
+          <t>2-s2.0-105037778677</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="C495" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr"/>
@@ -18347,19 +18347,19 @@
       </c>
       <c r="I495" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J495" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105037778677</t>
+          <t>2-s2.0-105038284296</t>
         </is>
       </c>
       <c r="B496" s="3" t="n">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr"/>
@@ -18375,7 +18375,7 @@
       <c r="F496" s="2" t="inlineStr"/>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H496" s="2" t="n">
@@ -18383,19 +18383,19 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Adolfo Baltar Moreno</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038284296</t>
+          <t>2-s2.0-105038736824</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="C497" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr"/>
@@ -18411,7 +18411,7 @@
       <c r="F497" s="4" t="inlineStr"/>
       <c r="G497" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H497" s="4" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="I497" s="4" t="inlineStr">
         <is>
-          <t>Adolfo Baltar Moreno</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J497" s="4" t="inlineStr">
@@ -18431,7 +18431,7 @@
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038736824</t>
+          <t>2-s2.0-105038742372</t>
         </is>
       </c>
       <c r="B498" s="3" t="n">
@@ -18467,7 +18467,7 @@
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038742372</t>
+          <t>2-s2.0-105038743806</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
@@ -18503,7 +18503,7 @@
     <row r="500" ht="16" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038743806</t>
+          <t>2-s2.0-105038765565</t>
         </is>
       </c>
       <c r="B500" s="3" t="n">
@@ -18539,7 +18539,7 @@
     <row r="501" ht="16" customHeight="1">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038765565</t>
+          <t>2-s2.0-85184473223</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="C501" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr"/>
@@ -18555,7 +18555,7 @@
       <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H501" s="4" t="n">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="I501" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
         </is>
       </c>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="502" ht="16" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85184473223</t>
+          <t>2-s2.0-85196638440</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
@@ -18599,19 +18599,19 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Jeovanny de Jesus Muentes Acevedo</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="503" ht="16" customHeight="1">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85196638440</t>
+          <t>2-s2.0-85203247315</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="C503" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr"/>
@@ -18635,19 +18635,19 @@
       </c>
       <c r="I503" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="504" ht="16" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85203247315</t>
+          <t>2-s2.0-85204485969</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr"/>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
     <row r="505" ht="16" customHeight="1">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85204485969</t>
+          <t>2-s2.0-85204899789</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -18699,7 +18699,7 @@
       <c r="F505" s="4" t="inlineStr"/>
       <c r="G505" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H505" s="4" t="n">
@@ -18707,19 +18707,19 @@
       </c>
       <c r="I505" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="506" ht="16" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85204899789</t>
+          <t>2-s2.0-85207831270</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr"/>
@@ -18735,7 +18735,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H506" s="2" t="n">
@@ -18743,19 +18743,19 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85207831270</t>
+          <t>2-s2.0-85207842768</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="I507" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J507" s="4" t="inlineStr">
@@ -18791,7 +18791,7 @@
     <row r="508" ht="16" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85207842768</t>
+          <t>2-s2.0-85208015450</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -18827,7 +18827,7 @@
     <row r="509" ht="16" customHeight="1">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85208015450</t>
+          <t>2-s2.0-85208026562</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="I509" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J509" s="4" t="inlineStr">
@@ -18863,7 +18863,7 @@
     <row r="510" ht="16" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85208026562</t>
+          <t>2-s2.0-85209250813</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
       <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H510" s="2" t="n">
@@ -18887,19 +18887,19 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="511" ht="16" customHeight="1">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85209250813</t>
+          <t>2-s2.0-85212267636</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
@@ -18923,19 +18923,19 @@
       </c>
       <c r="I511" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="512" ht="16" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85212267636</t>
+          <t>2-s2.0-85212831235</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
@@ -18951,7 +18951,7 @@
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H512" s="2" t="n">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -18971,7 +18971,7 @@
     <row r="513" ht="16" customHeight="1">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85212831235</t>
+          <t>2-s2.0-85213079490</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
@@ -18987,7 +18987,7 @@
       <c r="F513" s="4" t="inlineStr"/>
       <c r="G513" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H513" s="4" t="n">
@@ -18995,19 +18995,19 @@
       </c>
       <c r="I513" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="514" ht="16" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079490</t>
+          <t>2-s2.0-85213079633</t>
         </is>
       </c>
       <c r="B514" s="3" t="n">
@@ -19023,7 +19023,7 @@
       <c r="F514" s="2" t="inlineStr"/>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H514" s="2" t="n">
@@ -19031,19 +19031,19 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="515" ht="16" customHeight="1">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079633</t>
+          <t>2-s2.0-85213083915</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
@@ -19067,19 +19067,19 @@
       </c>
       <c r="I515" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="516" ht="16" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213083915</t>
+          <t>2-s2.0-85214707412</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
@@ -19115,7 +19115,7 @@
     <row r="517" ht="16" customHeight="1">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85214707412</t>
+          <t>2-s2.0-85215238378</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
@@ -19131,7 +19131,7 @@
       <c r="F517" s="4" t="inlineStr"/>
       <c r="G517" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H517" s="4" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="I517" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J517" s="4" t="inlineStr">
@@ -19151,7 +19151,7 @@
     <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85215238378</t>
+          <t>2-s2.0-85215371893</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">
@@ -19167,7 +19167,7 @@
       <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H518" s="2" t="n">
@@ -19175,19 +19175,19 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="519" ht="16" customHeight="1">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85215371893</t>
+          <t>2-s2.0-85218385938</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="C519" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr"/>
@@ -19203,7 +19203,7 @@
       <c r="F519" s="4" t="inlineStr"/>
       <c r="G519" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H519" s="4" t="n">
@@ -19211,19 +19211,19 @@
       </c>
       <c r="I519" s="4" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="520" ht="16" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85218385938</t>
+          <t>2-s2.0-85219053945</t>
         </is>
       </c>
       <c r="B520" s="3" t="n">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H520" s="2" t="n">
@@ -19247,19 +19247,19 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="521" ht="16" customHeight="1">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85219053945</t>
+          <t>2-s2.0-86000303183</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -19275,7 +19275,7 @@
       <c r="F521" s="4" t="inlineStr"/>
       <c r="G521" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H521" s="4" t="n">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="I521" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="J521" s="4" t="inlineStr">
@@ -19295,7 +19295,7 @@
     <row r="522" ht="16" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000303183</t>
+          <t>2-s2.0-86000354258</t>
         </is>
       </c>
       <c r="B522" s="3" t="n">
@@ -19311,7 +19311,7 @@
       <c r="F522" s="2" t="inlineStr"/>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H522" s="2" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -19331,7 +19331,7 @@
     <row r="523" ht="16" customHeight="1">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-86000354258</t>
+          <t>2-s2.0-86000451627</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="C523" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr"/>
@@ -19347,7 +19347,7 @@
       <c r="F523" s="4" t="inlineStr"/>
       <c r="G523" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H523" s="4" t="n">
@@ -19355,27 +19355,27 @@
       </c>
       <c r="I523" s="4" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000451627</t>
+          <t>2-s2.0-105007361101</t>
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr"/>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -21668,8 +21668,44 @@
         </is>
       </c>
     </row>
+    <row r="588" ht="16" customHeight="1">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105045219323</t>
+        </is>
+      </c>
+      <c r="B588" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C588" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr"/>
+      <c r="E588" s="3" t="inlineStr"/>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J587"/>
+  <autoFilter ref="A1:J588"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21913,10 +21949,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>106</v>
@@ -21931,7 +21967,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>12</v>
@@ -21944,12 +21980,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -21960,10 +21996,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>9</v>
@@ -21975,10 +22011,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>7</v>
@@ -21991,12 +22027,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -22148,10 +22184,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>126</v>
@@ -22163,7 +22199,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>27</v>
@@ -22179,7 +22215,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22580,13 +22616,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>9</v>
@@ -22602,7 +22638,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -22154,23 +22154,23 @@
         <v>17</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -22202,20 +22202,20 @@
         <v>46</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22244,23 +22244,23 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>18</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -22289,23 +22289,23 @@
         <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
@@ -22497,7 +22497,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>26325154200</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
         <v>73</v>
       </c>
@@ -22508,20 +22512,20 @@
         <v>3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -22536,7 +22540,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>57202285682</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n">
         <v>65</v>
       </c>
@@ -22547,20 +22555,20 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22583,11 @@
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>24329839300</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
         <v>46</v>
       </c>
@@ -22583,23 +22595,23 @@
         <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -22614,7 +22626,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>57191333650</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="n">
         <v>35</v>
       </c>
@@ -22634,7 +22650,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
@@ -22653,7 +22669,11 @@
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>57210822856</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n">
         <v>32</v>
       </c>
@@ -22670,14 +22690,14 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22712,11 @@
           <t>Ciencias Básicas</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>56674579200</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="n">
         <v>31</v>
       </c>
@@ -22700,10 +22724,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0</v>
@@ -22712,11 +22736,11 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22755,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>57156565000</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n">
         <v>31</v>
       </c>
@@ -22751,7 +22779,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -22770,7 +22798,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>57220927199</t>
+        </is>
+      </c>
       <c r="D9" s="4" t="n">
         <v>29</v>
       </c>
@@ -22781,20 +22813,20 @@
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -22809,7 +22841,11 @@
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>7005142049</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
         <v>28</v>
       </c>
@@ -22817,7 +22853,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -22826,14 +22862,14 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22884,11 @@
           <t>Ciencias Básicas</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>36142156300</t>
+        </is>
+      </c>
       <c r="D11" s="4" t="n">
         <v>24</v>
       </c>
@@ -22856,7 +22896,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>1</v>
@@ -22865,14 +22905,14 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -22887,7 +22927,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>35788581800</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
@@ -22901,17 +22945,17 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -22926,7 +22970,11 @@
           <t>Escuela de Transformación Digital</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>57193012270</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="n">
         <v>21</v>
       </c>
@@ -22940,7 +22988,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>2</v>
@@ -22950,7 +22998,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -22965,7 +23013,11 @@
           <t>Ciencias Básicas</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>55649334800</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
         <v>20</v>
       </c>
@@ -22973,10 +23025,10 @@
         <v>5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -22985,11 +23037,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23056,11 @@
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>57194034904</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="n">
         <v>18</v>
       </c>
@@ -23024,7 +23080,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -23043,7 +23099,11 @@
           <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>57196040759</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
         <v>18</v>
       </c>
@@ -23060,14 +23120,14 @@
         <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -23082,7 +23142,11 @@
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>56581610900</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n">
         <v>17</v>
       </c>
@@ -23093,7 +23157,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>2</v>
@@ -23102,11 +23166,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -23121,7 +23185,11 @@
           <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>57930948900</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
         <v>17</v>
       </c>
@@ -23141,7 +23209,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -23160,7 +23228,11 @@
           <t>Ciencias Básicas</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>57220077867</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="n">
         <v>16</v>
       </c>
@@ -23177,14 +23249,14 @@
         <v>0</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -23199,7 +23271,11 @@
           <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>57192930752</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
         <v>16</v>
       </c>
@@ -23219,7 +23295,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -23238,7 +23314,11 @@
           <t>Ciencias Básicas</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>57190688459</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="n">
         <v>15</v>
       </c>
@@ -23255,10 +23335,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Docentes activos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$588</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB'!$A$1:$J$591</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J588"/>
+  <dimension ref="A1:J591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18539,7 +18539,7 @@
     <row r="501" ht="16" customHeight="1">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85184473223</t>
+          <t>2-s2.0-105045743544</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -18555,7 +18555,7 @@
       <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H501" s="4" t="n">
@@ -18563,19 +18563,19 @@
       </c>
       <c r="I501" s="4" t="inlineStr">
         <is>
-          <t>Jeovanny de Jesus Muentes Acevedo</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="502" ht="16" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85196638440</t>
+          <t>2-s2.0-85184473223</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
@@ -18599,19 +18599,19 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="503" ht="16" customHeight="1">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85203247315</t>
+          <t>2-s2.0-85196638440</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="C503" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr"/>
@@ -18635,19 +18635,19 @@
       </c>
       <c r="I503" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="504" ht="16" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85204485969</t>
+          <t>2-s2.0-85203247315</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr"/>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
     <row r="505" ht="16" customHeight="1">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85204899789</t>
+          <t>2-s2.0-85204485969</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -18699,7 +18699,7 @@
       <c r="F505" s="4" t="inlineStr"/>
       <c r="G505" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H505" s="4" t="n">
@@ -18707,19 +18707,19 @@
       </c>
       <c r="I505" s="4" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="506" ht="16" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85207831270</t>
+          <t>2-s2.0-85204899789</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr"/>
@@ -18735,7 +18735,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H506" s="2" t="n">
@@ -18743,19 +18743,19 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85207842768</t>
+          <t>2-s2.0-85207831270</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="I507" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J507" s="4" t="inlineStr">
@@ -18791,7 +18791,7 @@
     <row r="508" ht="16" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85208015450</t>
+          <t>2-s2.0-85207842768</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -18827,7 +18827,7 @@
     <row r="509" ht="16" customHeight="1">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85208026562</t>
+          <t>2-s2.0-85208015450</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="I509" s="4" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J509" s="4" t="inlineStr">
@@ -18863,7 +18863,7 @@
     <row r="510" ht="16" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85209250813</t>
+          <t>2-s2.0-85208026562</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
       <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H510" s="2" t="n">
@@ -18887,19 +18887,19 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="511" ht="16" customHeight="1">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85212267636</t>
+          <t>2-s2.0-85209250813</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
@@ -18923,19 +18923,19 @@
       </c>
       <c r="I511" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="512" ht="16" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85212831235</t>
+          <t>2-s2.0-85212267636</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
@@ -18951,7 +18951,7 @@
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H512" s="2" t="n">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -18971,7 +18971,7 @@
     <row r="513" ht="16" customHeight="1">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079490</t>
+          <t>2-s2.0-85212831235</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
@@ -18987,7 +18987,7 @@
       <c r="F513" s="4" t="inlineStr"/>
       <c r="G513" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H513" s="4" t="n">
@@ -18995,19 +18995,19 @@
       </c>
       <c r="I513" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="514" ht="16" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079633</t>
+          <t>2-s2.0-85213079490</t>
         </is>
       </c>
       <c r="B514" s="3" t="n">
@@ -19023,7 +19023,7 @@
       <c r="F514" s="2" t="inlineStr"/>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H514" s="2" t="n">
@@ -19031,19 +19031,19 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="515" ht="16" customHeight="1">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85213083915</t>
+          <t>2-s2.0-85213079633</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
@@ -19067,19 +19067,19 @@
       </c>
       <c r="I515" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="516" ht="16" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85214707412</t>
+          <t>2-s2.0-85213083915</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
@@ -19115,7 +19115,7 @@
     <row r="517" ht="16" customHeight="1">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85215238378</t>
+          <t>2-s2.0-85214707412</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
@@ -19131,7 +19131,7 @@
       <c r="F517" s="4" t="inlineStr"/>
       <c r="G517" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H517" s="4" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="I517" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J517" s="4" t="inlineStr">
@@ -19151,7 +19151,7 @@
     <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85215371893</t>
+          <t>2-s2.0-85215238378</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">
@@ -19167,7 +19167,7 @@
       <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H518" s="2" t="n">
@@ -19175,19 +19175,19 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="519" ht="16" customHeight="1">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85218385938</t>
+          <t>2-s2.0-85215371893</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="C519" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr"/>
@@ -19203,7 +19203,7 @@
       <c r="F519" s="4" t="inlineStr"/>
       <c r="G519" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H519" s="4" t="n">
@@ -19211,19 +19211,19 @@
       </c>
       <c r="I519" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="520" ht="16" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85219053945</t>
+          <t>2-s2.0-85218385938</t>
         </is>
       </c>
       <c r="B520" s="3" t="n">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H520" s="2" t="n">
@@ -19247,19 +19247,19 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="521" ht="16" customHeight="1">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-86000303183</t>
+          <t>2-s2.0-85219053945</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -19275,7 +19275,7 @@
       <c r="F521" s="4" t="inlineStr"/>
       <c r="G521" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H521" s="4" t="n">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="I521" s="4" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J521" s="4" t="inlineStr">
@@ -19295,7 +19295,7 @@
     <row r="522" ht="16" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000354258</t>
+          <t>2-s2.0-86000303183</t>
         </is>
       </c>
       <c r="B522" s="3" t="n">
@@ -19311,7 +19311,7 @@
       <c r="F522" s="2" t="inlineStr"/>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H522" s="2" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -19331,7 +19331,7 @@
     <row r="523" ht="16" customHeight="1">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-86000451627</t>
+          <t>2-s2.0-86000354258</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="C523" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr"/>
@@ -19347,7 +19347,7 @@
       <c r="F523" s="4" t="inlineStr"/>
       <c r="G523" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H523" s="4" t="n">
@@ -19355,27 +19355,27 @@
       </c>
       <c r="I523" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105007361101</t>
+          <t>2-s2.0-86000451627</t>
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr"/>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -19403,7 +19403,7 @@
     <row r="525" ht="16" customHeight="1">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105013662781</t>
+          <t>2-s2.0-105007361101</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
@@ -19419,7 +19419,7 @@
       <c r="F525" s="4" t="inlineStr"/>
       <c r="G525" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H525" s="4" t="n">
@@ -19427,19 +19427,19 @@
       </c>
       <c r="I525" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J525" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="526" ht="16" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105016249780</t>
+          <t>2-s2.0-105013662781</t>
         </is>
       </c>
       <c r="B526" s="3" t="n">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr"/>
@@ -19455,7 +19455,7 @@
       <c r="F526" s="2" t="inlineStr"/>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H526" s="2" t="n">
@@ -19463,19 +19463,19 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="527" ht="16" customHeight="1">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105017763405</t>
+          <t>2-s2.0-105016249780</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C527" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr"/>
@@ -19491,7 +19491,7 @@
       <c r="F527" s="4" t="inlineStr"/>
       <c r="G527" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H527" s="4" t="n">
@@ -19499,19 +19499,19 @@
       </c>
       <c r="I527" s="4" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J527" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="528" ht="16" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020672925</t>
+          <t>2-s2.0-105017763405</t>
         </is>
       </c>
       <c r="B528" s="3" t="n">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr"/>
@@ -19527,7 +19527,7 @@
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H528" s="2" t="n">
@@ -19535,19 +19535,19 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="529" ht="16" customHeight="1">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020779857</t>
+          <t>2-s2.0-105020672925</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
@@ -19571,19 +19571,19 @@
       </c>
       <c r="I529" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J529" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="530" ht="16" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020787948</t>
+          <t>2-s2.0-105020779857</t>
         </is>
       </c>
       <c r="B530" s="3" t="n">
@@ -19607,19 +19607,19 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="531" ht="16" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020807503</t>
+          <t>2-s2.0-105020787948</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="I531" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J531" s="4" t="inlineStr">
@@ -19655,7 +19655,7 @@
     <row r="532" ht="16" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105023273177</t>
+          <t>2-s2.0-105020807503</t>
         </is>
       </c>
       <c r="B532" s="3" t="n">
@@ -19671,7 +19671,7 @@
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H532" s="2" t="n">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr">
@@ -19691,7 +19691,7 @@
     <row r="533" ht="16" customHeight="1">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105023274545</t>
+          <t>2-s2.0-105023273177</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -19727,7 +19727,7 @@
     <row r="534" ht="16" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105024867073</t>
+          <t>2-s2.0-105023274545</t>
         </is>
       </c>
       <c r="B534" s="3" t="n">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr"/>
@@ -19743,7 +19743,7 @@
       <c r="F534" s="2" t="inlineStr"/>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H534" s="2" t="n">
@@ -19751,19 +19751,19 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="535" ht="16" customHeight="1">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105027320140</t>
+          <t>2-s2.0-105024867073</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -19779,7 +19779,7 @@
       <c r="F535" s="4" t="inlineStr"/>
       <c r="G535" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H535" s="4" t="n">
@@ -19787,19 +19787,19 @@
       </c>
       <c r="I535" s="4" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J535" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="536" ht="16" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105027841808</t>
+          <t>2-s2.0-105027320140</t>
         </is>
       </c>
       <c r="B536" s="3" t="n">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
@@ -19835,7 +19835,7 @@
     <row r="537" ht="16" customHeight="1">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028108336</t>
+          <t>2-s2.0-105027841808</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="C537" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr"/>
@@ -19859,19 +19859,19 @@
       </c>
       <c r="I537" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="538" ht="16" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028439729</t>
+          <t>2-s2.0-105028108336</t>
         </is>
       </c>
       <c r="B538" s="3" t="n">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr"/>
@@ -19887,7 +19887,7 @@
       <c r="F538" s="2" t="inlineStr"/>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H538" s="2" t="n">
@@ -19895,19 +19895,19 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="539" ht="16" customHeight="1">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028658534</t>
+          <t>2-s2.0-105028439729</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr"/>
@@ -19923,7 +19923,7 @@
       <c r="F539" s="4" t="inlineStr"/>
       <c r="G539" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H539" s="4" t="n">
@@ -19931,19 +19931,19 @@
       </c>
       <c r="I539" s="4" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J539" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="540" ht="16" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028891498</t>
+          <t>2-s2.0-105028658534</t>
         </is>
       </c>
       <c r="B540" s="3" t="n">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr"/>
@@ -19959,7 +19959,7 @@
       <c r="F540" s="2" t="inlineStr"/>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H540" s="2" t="n">
@@ -19967,19 +19967,19 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="541" ht="16" customHeight="1">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028921643</t>
+          <t>2-s2.0-105028891498</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -19995,7 +19995,7 @@
       <c r="F541" s="4" t="inlineStr"/>
       <c r="G541" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H541" s="4" t="n">
@@ -20003,19 +20003,19 @@
       </c>
       <c r="I541" s="4" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
         </is>
       </c>
       <c r="J541" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="542" ht="16" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029250747</t>
+          <t>2-s2.0-105028921643</t>
         </is>
       </c>
       <c r="B542" s="3" t="n">
@@ -20023,7 +20023,7 @@
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr"/>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr">
@@ -20051,7 +20051,7 @@
     <row r="543" ht="16" customHeight="1">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029263427</t>
+          <t>2-s2.0-105029250747</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C543" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr"/>
@@ -20075,7 +20075,7 @@
       </c>
       <c r="I543" s="4" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J543" s="4" t="inlineStr">
@@ -20087,7 +20087,7 @@
     <row r="544" ht="16" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029346081</t>
+          <t>2-s2.0-105029263427</t>
         </is>
       </c>
       <c r="B544" s="3" t="n">
@@ -20103,7 +20103,7 @@
       <c r="F544" s="2" t="inlineStr"/>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H544" s="2" t="n">
@@ -20111,19 +20111,19 @@
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="545" ht="16" customHeight="1">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029819163</t>
+          <t>2-s2.0-105029346081</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
@@ -20139,7 +20139,7 @@
       <c r="F545" s="4" t="inlineStr"/>
       <c r="G545" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H545" s="4" t="n">
@@ -20147,19 +20147,19 @@
       </c>
       <c r="I545" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="546" ht="16" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029861079</t>
+          <t>2-s2.0-105029819163</t>
         </is>
       </c>
       <c r="B546" s="3" t="n">
@@ -20175,7 +20175,7 @@
       <c r="F546" s="2" t="inlineStr"/>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H546" s="2" t="n">
@@ -20183,19 +20183,19 @@
       </c>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="547" ht="16" customHeight="1">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105030266202</t>
+          <t>2-s2.0-105029861079</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
@@ -20211,7 +20211,7 @@
       <c r="F547" s="4" t="inlineStr"/>
       <c r="G547" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H547" s="4" t="n">
@@ -20219,19 +20219,19 @@
       </c>
       <c r="I547" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="J547" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="548" ht="16" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031262073</t>
+          <t>2-s2.0-105030266202</t>
         </is>
       </c>
       <c r="B548" s="3" t="n">
@@ -20267,7 +20267,7 @@
     <row r="549" ht="16" customHeight="1">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031578343</t>
+          <t>2-s2.0-105031262073</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
@@ -20283,7 +20283,7 @@
       <c r="F549" s="4" t="inlineStr"/>
       <c r="G549" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H549" s="4" t="n">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="I549" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J549" s="4" t="inlineStr">
@@ -20303,7 +20303,7 @@
     <row r="550" ht="16" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031596663</t>
+          <t>2-s2.0-105031578343</t>
         </is>
       </c>
       <c r="B550" s="3" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr"/>
@@ -20319,7 +20319,7 @@
       <c r="F550" s="2" t="inlineStr"/>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H550" s="2" t="n">
@@ -20327,19 +20327,19 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="551" ht="16" customHeight="1">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033266676</t>
+          <t>2-s2.0-105031596663</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="C551" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr"/>
@@ -20355,7 +20355,7 @@
       <c r="F551" s="4" t="inlineStr"/>
       <c r="G551" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H551" s="4" t="n">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="I551" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J551" s="4" t="inlineStr">
@@ -20375,7 +20375,7 @@
     <row r="552" ht="16" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033689829</t>
+          <t>2-s2.0-105033266676</t>
         </is>
       </c>
       <c r="B552" s="3" t="n">
@@ -20399,19 +20399,19 @@
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="553" ht="16" customHeight="1">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033935110</t>
+          <t>2-s2.0-105033689829</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="I553" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J553" s="4" t="inlineStr">
@@ -20447,7 +20447,7 @@
     <row r="554" ht="16" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033998924</t>
+          <t>2-s2.0-105033935110</t>
         </is>
       </c>
       <c r="B554" s="3" t="n">
@@ -20463,7 +20463,7 @@
       <c r="F554" s="2" t="inlineStr"/>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H554" s="2" t="n">
@@ -20471,19 +20471,19 @@
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="555" ht="16" customHeight="1">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034105140</t>
+          <t>2-s2.0-105033998924</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
@@ -20499,7 +20499,7 @@
       <c r="F555" s="4" t="inlineStr"/>
       <c r="G555" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H555" s="4" t="n">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="I555" s="4" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J555" s="4" t="inlineStr">
@@ -20519,7 +20519,7 @@
     <row r="556" ht="16" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034275781</t>
+          <t>2-s2.0-105034105140</t>
         </is>
       </c>
       <c r="B556" s="3" t="n">
@@ -20543,19 +20543,19 @@
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="557" ht="16" customHeight="1">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034300666</t>
+          <t>2-s2.0-105034275781</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -20571,7 +20571,7 @@
       <c r="F557" s="4" t="inlineStr"/>
       <c r="G557" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H557" s="4" t="n">
@@ -20579,19 +20579,19 @@
       </c>
       <c r="I557" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J557" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="558" ht="16" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034470662</t>
+          <t>2-s2.0-105034300666</t>
         </is>
       </c>
       <c r="B558" s="3" t="n">
@@ -20607,7 +20607,7 @@
       <c r="F558" s="2" t="inlineStr"/>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H558" s="2" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -20627,7 +20627,7 @@
     <row r="559" ht="16" customHeight="1">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034590431</t>
+          <t>2-s2.0-105034470662</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -20643,7 +20643,7 @@
       <c r="F559" s="4" t="inlineStr"/>
       <c r="G559" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H559" s="4" t="n">
@@ -20651,19 +20651,19 @@
       </c>
       <c r="I559" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J559" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="560" ht="16" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035297301</t>
+          <t>2-s2.0-105034590431</t>
         </is>
       </c>
       <c r="B560" s="3" t="n">
@@ -20687,19 +20687,19 @@
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="561" ht="16" customHeight="1">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035301017</t>
+          <t>2-s2.0-105035297301</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -20723,19 +20723,19 @@
       </c>
       <c r="I561" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J561" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="562" ht="16" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035647006</t>
+          <t>2-s2.0-105035301017</t>
         </is>
       </c>
       <c r="B562" s="3" t="n">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr"/>
@@ -20759,19 +20759,19 @@
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="563" ht="16" customHeight="1">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035812865</t>
+          <t>2-s2.0-105035647006</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="C563" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr"/>
@@ -20787,7 +20787,7 @@
       <c r="F563" s="4" t="inlineStr"/>
       <c r="G563" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H563" s="4" t="n">
@@ -20795,19 +20795,19 @@
       </c>
       <c r="I563" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J563" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="564" ht="16" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105037520290</t>
+          <t>2-s2.0-105035812865</t>
         </is>
       </c>
       <c r="B564" s="3" t="n">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr"/>
@@ -20823,7 +20823,7 @@
       <c r="F564" s="2" t="inlineStr"/>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H564" s="2" t="n">
@@ -20831,19 +20831,19 @@
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="565" ht="16" customHeight="1">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105037554330</t>
+          <t>2-s2.0-105037520290</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C565" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr"/>
@@ -20859,7 +20859,7 @@
       <c r="F565" s="4" t="inlineStr"/>
       <c r="G565" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H565" s="4" t="n">
@@ -20867,19 +20867,19 @@
       </c>
       <c r="I565" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="J565" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="566" ht="16" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038191517</t>
+          <t>2-s2.0-105037554330</t>
         </is>
       </c>
       <c r="B566" s="3" t="n">
@@ -20895,7 +20895,7 @@
       <c r="F566" s="2" t="inlineStr"/>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H566" s="2" t="n">
@@ -20903,19 +20903,19 @@
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="567" ht="16" customHeight="1">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038213221</t>
+          <t>2-s2.0-105038191517</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
@@ -20931,7 +20931,7 @@
       <c r="F567" s="4" t="inlineStr"/>
       <c r="G567" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H567" s="4" t="n">
@@ -20939,19 +20939,19 @@
       </c>
       <c r="I567" s="4" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J567" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="568" ht="16" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038231274</t>
+          <t>2-s2.0-105038213221</t>
         </is>
       </c>
       <c r="B568" s="3" t="n">
@@ -20967,7 +20967,7 @@
       <c r="F568" s="2" t="inlineStr"/>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H568" s="2" t="n">
@@ -20975,19 +20975,19 @@
       </c>
       <c r="I568" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="569" ht="16" customHeight="1">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038348383</t>
+          <t>2-s2.0-105038231274</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -21011,19 +21011,19 @@
       </c>
       <c r="I569" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J569" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="570" ht="16" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038667034</t>
+          <t>2-s2.0-105038348383</t>
         </is>
       </c>
       <c r="B570" s="3" t="n">
@@ -21039,7 +21039,7 @@
       <c r="F570" s="2" t="inlineStr"/>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H570" s="2" t="n">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J570" s="2" t="inlineStr">
@@ -21059,7 +21059,7 @@
     <row r="571" ht="16" customHeight="1">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040384895</t>
+          <t>2-s2.0-105038667034</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -21075,7 +21075,7 @@
       <c r="F571" s="4" t="inlineStr"/>
       <c r="G571" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H571" s="4" t="n">
@@ -21083,19 +21083,19 @@
       </c>
       <c r="I571" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J571" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="572" ht="16" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040648386</t>
+          <t>2-s2.0-105040384895</t>
         </is>
       </c>
       <c r="B572" s="3" t="n">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J572" s="2" t="inlineStr">
@@ -21131,7 +21131,7 @@
     <row r="573" ht="16" customHeight="1">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040720975</t>
+          <t>2-s2.0-105040648386</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr"/>
@@ -21147,7 +21147,7 @@
       <c r="F573" s="4" t="inlineStr"/>
       <c r="G573" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H573" s="4" t="n">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="I573" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J573" s="4" t="inlineStr">
@@ -21167,7 +21167,7 @@
     <row r="574" ht="16" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040813266</t>
+          <t>2-s2.0-105040720975</t>
         </is>
       </c>
       <c r="B574" s="3" t="n">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr"/>
@@ -21183,7 +21183,7 @@
       <c r="F574" s="2" t="inlineStr"/>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H574" s="2" t="n">
@@ -21191,19 +21191,19 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="575" ht="16" customHeight="1">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040833810</t>
+          <t>2-s2.0-105040813266</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -21227,19 +21227,19 @@
       </c>
       <c r="I575" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J575" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="576" ht="16" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040999318</t>
+          <t>2-s2.0-105040833810</t>
         </is>
       </c>
       <c r="B576" s="3" t="n">
@@ -21255,7 +21255,7 @@
       <c r="F576" s="2" t="inlineStr"/>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H576" s="2" t="n">
@@ -21263,19 +21263,19 @@
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="577" ht="16" customHeight="1">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041019868</t>
+          <t>2-s2.0-105040999318</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
@@ -21291,7 +21291,7 @@
       <c r="F577" s="4" t="inlineStr"/>
       <c r="G577" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H577" s="4" t="n">
@@ -21299,19 +21299,19 @@
       </c>
       <c r="I577" s="4" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="J577" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="578" ht="16" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041022111</t>
+          <t>2-s2.0-105041019868</t>
         </is>
       </c>
       <c r="B578" s="3" t="n">
@@ -21327,7 +21327,7 @@
       <c r="F578" s="2" t="inlineStr"/>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H578" s="2" t="n">
@@ -21335,19 +21335,19 @@
       </c>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="579" ht="16" customHeight="1">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041142576</t>
+          <t>2-s2.0-105041022111</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -21363,7 +21363,7 @@
       <c r="F579" s="4" t="inlineStr"/>
       <c r="G579" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H579" s="4" t="n">
@@ -21371,19 +21371,19 @@
       </c>
       <c r="I579" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J579" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="580" ht="16" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041927617</t>
+          <t>2-s2.0-105041142576</t>
         </is>
       </c>
       <c r="B580" s="3" t="n">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
       <c r="F580" s="2" t="inlineStr"/>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H580" s="2" t="n">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J580" s="2" t="inlineStr">
@@ -21419,7 +21419,7 @@
     <row r="581" ht="16" customHeight="1">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105042109693</t>
+          <t>2-s2.0-105041927617</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -21427,7 +21427,7 @@
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr"/>
@@ -21435,7 +21435,7 @@
       <c r="F581" s="4" t="inlineStr"/>
       <c r="G581" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H581" s="4" t="n">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="I581" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J581" s="4" t="inlineStr">
@@ -21455,7 +21455,7 @@
     <row r="582" ht="16" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042557607</t>
+          <t>2-s2.0-105042109693</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr">
@@ -21491,7 +21491,7 @@
     <row r="583" ht="16" customHeight="1">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105042877513</t>
+          <t>2-s2.0-105042557607</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="I583" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J583" s="4" t="inlineStr">
@@ -21527,7 +21527,7 @@
     <row r="584" ht="16" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105043654106</t>
+          <t>2-s2.0-105042877513</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr">
@@ -21563,7 +21563,7 @@
     <row r="585" ht="16" customHeight="1">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044659449</t>
+          <t>2-s2.0-105043654106</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -21579,7 +21579,7 @@
       <c r="F585" s="4" t="inlineStr"/>
       <c r="G585" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H585" s="4" t="n">
@@ -21587,19 +21587,19 @@
       </c>
       <c r="I585" s="4" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J585" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="586" ht="16" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105044699156</t>
+          <t>2-s2.0-105044659449</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
@@ -21623,19 +21623,19 @@
       </c>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="587" ht="16" customHeight="1">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044735313</t>
+          <t>2-s2.0-105044663806</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -21651,7 +21651,7 @@
       <c r="F587" s="4" t="inlineStr"/>
       <c r="G587" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H587" s="4" t="n">
@@ -21659,19 +21659,19 @@
       </c>
       <c r="I587" s="4" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="J587" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="588" ht="16" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105045219323</t>
+          <t>2-s2.0-105044699156</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
@@ -21704,8 +21704,116 @@
         </is>
       </c>
     </row>
+    <row r="589" ht="16" customHeight="1">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105044735313</t>
+        </is>
+      </c>
+      <c r="B589" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D589" s="4" t="inlineStr"/>
+      <c r="E589" s="5" t="inlineStr"/>
+      <c r="F589" s="4" t="inlineStr"/>
+      <c r="G589" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H589" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I589" s="4" t="inlineStr">
+        <is>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
+        </is>
+      </c>
+      <c r="J589" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="16" customHeight="1">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105045219323</t>
+        </is>
+      </c>
+      <c r="B590" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C590" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr"/>
+      <c r="E590" s="3" t="inlineStr"/>
+      <c r="F590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="16" customHeight="1">
+      <c r="A591" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105045927756</t>
+        </is>
+      </c>
+      <c r="B591" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D591" s="4" t="inlineStr"/>
+      <c r="E591" s="5" t="inlineStr"/>
+      <c r="F591" s="4" t="inlineStr"/>
+      <c r="G591" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H591" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I591" s="4" t="inlineStr">
+        <is>
+          <t>Andres Guillermo Marrugo Hernandez</t>
+        </is>
+      </c>
+      <c r="J591" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J588"/>
+  <autoFilter ref="A1:J591"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21949,10 +22057,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>106</v>
@@ -21970,7 +22078,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>3</v>
@@ -21980,12 +22088,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -21996,10 +22104,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>9</v>
@@ -22008,10 +22116,10 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>14</v>
@@ -22027,12 +22135,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22247,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>96</v>
@@ -22151,7 +22259,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>55</v>
@@ -22160,7 +22268,7 @@
         <v>29</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>26</v>
@@ -22170,7 +22278,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -22184,10 +22292,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>126</v>
@@ -22199,7 +22307,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>30</v>
@@ -22215,7 +22323,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -22229,10 +22337,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -22250,7 +22358,7 @@
         <v>18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>18</v>
@@ -22260,7 +22368,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -22589,7 +22697,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>10</v>
@@ -22601,7 +22709,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>4</v>
@@ -22611,7 +22719,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -23048,86 +23156,86 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Holman Ospina Mateus</t>
+          <t>Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>57194034904</t>
+          <t>57196040759</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Holman Ospina Mateus</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>57196040759</t>
+          <t>57194034904</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>18</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="H16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Artículos UTB (SJR)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artículos UTB (CS)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen por año (SJR)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen por año (CS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumen por Escuela (SJR)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumen por Escuela (CS)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$591</definedName>
@@ -43676,86 +43676,86 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>57156565000</t>
+          <t>56674579200</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>56674579200</t>
+          <t>57156565000</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -43848,86 +43848,86 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>35788581800</t>
+          <t>36142156300</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Lenny Alexandra Romero Perez</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>36142156300</t>
+          <t>35788581800</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -44192,86 +44192,86 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Vilma Viviana Ojeda Caicedo</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>57192930752</t>
+          <t>57220077867</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="J19" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Vilma Viviana Ojeda Caicedo</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>57220077867</t>
+          <t>57192930752</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>16</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>

--- a/tables.xlsx
+++ b/tables.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Docentes activos" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$591</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$591</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artículos UTB (SJR)'!$A$1:$J$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artículos UTB (CS)'!$A$1:$J$595</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J591"/>
+  <dimension ref="A1:J595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18567,7 +18567,7 @@
     <row r="501" ht="16" customHeight="1">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105045743544</t>
+          <t>2-s2.0-85184473223</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -18583,7 +18583,7 @@
       <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H501" s="4" t="n">
@@ -18591,19 +18591,19 @@
       </c>
       <c r="I501" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
         </is>
       </c>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="502" ht="16" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85184473223</t>
+          <t>2-s2.0-85196638440</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
@@ -18627,19 +18627,19 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Jeovanny de Jesus Muentes Acevedo</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="503" ht="16" customHeight="1">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85196638440</t>
+          <t>2-s2.0-85203247315</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="C503" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr"/>
@@ -18663,19 +18663,19 @@
       </c>
       <c r="I503" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="504" ht="16" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85203247315</t>
+          <t>2-s2.0-85204485969</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr"/>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -18711,7 +18711,7 @@
     <row r="505" ht="16" customHeight="1">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85204485969</t>
+          <t>2-s2.0-85204899789</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -18727,7 +18727,7 @@
       <c r="F505" s="4" t="inlineStr"/>
       <c r="G505" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H505" s="4" t="n">
@@ -18735,19 +18735,19 @@
       </c>
       <c r="I505" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="506" ht="16" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85204899789</t>
+          <t>2-s2.0-85207831270</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr"/>
@@ -18763,7 +18763,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H506" s="2" t="n">
@@ -18771,19 +18771,19 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85207831270</t>
+          <t>2-s2.0-85207842768</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="I507" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J507" s="4" t="inlineStr">
@@ -18819,7 +18819,7 @@
     <row r="508" ht="16" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85207842768</t>
+          <t>2-s2.0-85208015450</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -18855,7 +18855,7 @@
     <row r="509" ht="16" customHeight="1">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85208015450</t>
+          <t>2-s2.0-85208026562</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="I509" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J509" s="4" t="inlineStr">
@@ -18891,7 +18891,7 @@
     <row r="510" ht="16" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85208026562</t>
+          <t>2-s2.0-85209250813</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr"/>
@@ -18907,7 +18907,7 @@
       <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H510" s="2" t="n">
@@ -18915,19 +18915,19 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="511" ht="16" customHeight="1">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85209250813</t>
+          <t>2-s2.0-85212267636</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
@@ -18951,19 +18951,19 @@
       </c>
       <c r="I511" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="512" ht="16" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85212267636</t>
+          <t>2-s2.0-85212831235</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
@@ -18979,7 +18979,7 @@
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H512" s="2" t="n">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -18999,7 +18999,7 @@
     <row r="513" ht="16" customHeight="1">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85212831235</t>
+          <t>2-s2.0-85213079490</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
@@ -19015,7 +19015,7 @@
       <c r="F513" s="4" t="inlineStr"/>
       <c r="G513" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H513" s="4" t="n">
@@ -19023,19 +19023,19 @@
       </c>
       <c r="I513" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="514" ht="16" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079490</t>
+          <t>2-s2.0-85213079633</t>
         </is>
       </c>
       <c r="B514" s="3" t="n">
@@ -19051,7 +19051,7 @@
       <c r="F514" s="2" t="inlineStr"/>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H514" s="2" t="n">
@@ -19059,19 +19059,19 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="515" ht="16" customHeight="1">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079633</t>
+          <t>2-s2.0-85213083915</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
@@ -19095,19 +19095,19 @@
       </c>
       <c r="I515" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="516" ht="16" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213083915</t>
+          <t>2-s2.0-85214707412</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
@@ -19143,7 +19143,7 @@
     <row r="517" ht="16" customHeight="1">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85214707412</t>
+          <t>2-s2.0-85215238378</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
@@ -19159,7 +19159,7 @@
       <c r="F517" s="4" t="inlineStr"/>
       <c r="G517" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H517" s="4" t="n">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="I517" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J517" s="4" t="inlineStr">
@@ -19179,7 +19179,7 @@
     <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85215238378</t>
+          <t>2-s2.0-85215371893</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">
@@ -19195,7 +19195,7 @@
       <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H518" s="2" t="n">
@@ -19203,19 +19203,19 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="519" ht="16" customHeight="1">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85215371893</t>
+          <t>2-s2.0-85218385938</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="C519" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr"/>
@@ -19231,7 +19231,7 @@
       <c r="F519" s="4" t="inlineStr"/>
       <c r="G519" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H519" s="4" t="n">
@@ -19239,19 +19239,19 @@
       </c>
       <c r="I519" s="4" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="520" ht="16" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85218385938</t>
+          <t>2-s2.0-85219053945</t>
         </is>
       </c>
       <c r="B520" s="3" t="n">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr"/>
@@ -19267,7 +19267,7 @@
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H520" s="2" t="n">
@@ -19275,19 +19275,19 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="521" ht="16" customHeight="1">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85219053945</t>
+          <t>2-s2.0-86000303183</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -19303,7 +19303,7 @@
       <c r="F521" s="4" t="inlineStr"/>
       <c r="G521" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H521" s="4" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="I521" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="J521" s="4" t="inlineStr">
@@ -19323,7 +19323,7 @@
     <row r="522" ht="16" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000303183</t>
+          <t>2-s2.0-86000354258</t>
         </is>
       </c>
       <c r="B522" s="3" t="n">
@@ -19339,7 +19339,7 @@
       <c r="F522" s="2" t="inlineStr"/>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H522" s="2" t="n">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -19359,7 +19359,7 @@
     <row r="523" ht="16" customHeight="1">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-86000354258</t>
+          <t>2-s2.0-86000451627</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="C523" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr"/>
@@ -19375,7 +19375,7 @@
       <c r="F523" s="4" t="inlineStr"/>
       <c r="G523" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H523" s="4" t="n">
@@ -19383,27 +19383,27 @@
       </c>
       <c r="I523" s="4" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000451627</t>
+          <t>2-s2.0-105007361101</t>
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -19431,7 +19431,7 @@
     <row r="525" ht="16" customHeight="1">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105007361101</t>
+          <t>2-s2.0-105013662781</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
@@ -19447,7 +19447,7 @@
       <c r="F525" s="4" t="inlineStr"/>
       <c r="G525" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H525" s="4" t="n">
@@ -19455,19 +19455,19 @@
       </c>
       <c r="I525" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J525" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="526" ht="16" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105013662781</t>
+          <t>2-s2.0-105016249780</t>
         </is>
       </c>
       <c r="B526" s="3" t="n">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr"/>
@@ -19483,7 +19483,7 @@
       <c r="F526" s="2" t="inlineStr"/>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H526" s="2" t="n">
@@ -19491,19 +19491,19 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="527" ht="16" customHeight="1">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105016249780</t>
+          <t>2-s2.0-105017763405</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="C527" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr"/>
@@ -19519,7 +19519,7 @@
       <c r="F527" s="4" t="inlineStr"/>
       <c r="G527" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H527" s="4" t="n">
@@ -19527,19 +19527,19 @@
       </c>
       <c r="I527" s="4" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J527" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="528" ht="16" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105017763405</t>
+          <t>2-s2.0-105020672925</t>
         </is>
       </c>
       <c r="B528" s="3" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H528" s="2" t="n">
@@ -19563,19 +19563,19 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="529" ht="16" customHeight="1">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020672925</t>
+          <t>2-s2.0-105020779857</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
@@ -19599,19 +19599,19 @@
       </c>
       <c r="I529" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
         </is>
       </c>
       <c r="J529" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="530" ht="16" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020779857</t>
+          <t>2-s2.0-105020787948</t>
         </is>
       </c>
       <c r="B530" s="3" t="n">
@@ -19635,19 +19635,19 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="531" ht="16" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020787948</t>
+          <t>2-s2.0-105020807503</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="I531" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J531" s="4" t="inlineStr">
@@ -19683,7 +19683,7 @@
     <row r="532" ht="16" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020807503</t>
+          <t>2-s2.0-105023273177</t>
         </is>
       </c>
       <c r="B532" s="3" t="n">
@@ -19699,7 +19699,7 @@
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H532" s="2" t="n">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr">
@@ -19719,7 +19719,7 @@
     <row r="533" ht="16" customHeight="1">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105023273177</t>
+          <t>2-s2.0-105023274545</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -19755,7 +19755,7 @@
     <row r="534" ht="16" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105023274545</t>
+          <t>2-s2.0-105024867073</t>
         </is>
       </c>
       <c r="B534" s="3" t="n">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr"/>
@@ -19771,7 +19771,7 @@
       <c r="F534" s="2" t="inlineStr"/>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H534" s="2" t="n">
@@ -19779,19 +19779,19 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="535" ht="16" customHeight="1">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105024867073</t>
+          <t>2-s2.0-105027320140</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -19807,7 +19807,7 @@
       <c r="F535" s="4" t="inlineStr"/>
       <c r="G535" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H535" s="4" t="n">
@@ -19815,19 +19815,19 @@
       </c>
       <c r="I535" s="4" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
         </is>
       </c>
       <c r="J535" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="536" ht="16" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105027320140</t>
+          <t>2-s2.0-105027841808</t>
         </is>
       </c>
       <c r="B536" s="3" t="n">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
@@ -19863,7 +19863,7 @@
     <row r="537" ht="16" customHeight="1">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105027841808</t>
+          <t>2-s2.0-105028108336</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
@@ -19871,7 +19871,7 @@
       </c>
       <c r="C537" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr"/>
@@ -19887,19 +19887,19 @@
       </c>
       <c r="I537" s="4" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="538" ht="16" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028108336</t>
+          <t>2-s2.0-105028439729</t>
         </is>
       </c>
       <c r="B538" s="3" t="n">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr"/>
@@ -19915,7 +19915,7 @@
       <c r="F538" s="2" t="inlineStr"/>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H538" s="2" t="n">
@@ -19923,19 +19923,19 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="539" ht="16" customHeight="1">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028439729</t>
+          <t>2-s2.0-105028658534</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr"/>
@@ -19951,7 +19951,7 @@
       <c r="F539" s="4" t="inlineStr"/>
       <c r="G539" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H539" s="4" t="n">
@@ -19959,19 +19959,19 @@
       </c>
       <c r="I539" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="J539" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="540" ht="16" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028658534</t>
+          <t>2-s2.0-105028891498</t>
         </is>
       </c>
       <c r="B540" s="3" t="n">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr"/>
@@ -19987,7 +19987,7 @@
       <c r="F540" s="2" t="inlineStr"/>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H540" s="2" t="n">
@@ -19995,19 +19995,19 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="541" ht="16" customHeight="1">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028891498</t>
+          <t>2-s2.0-105028921643</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -20023,7 +20023,7 @@
       <c r="F541" s="4" t="inlineStr"/>
       <c r="G541" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H541" s="4" t="n">
@@ -20031,19 +20031,19 @@
       </c>
       <c r="I541" s="4" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J541" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="542" ht="16" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028921643</t>
+          <t>2-s2.0-105029250747</t>
         </is>
       </c>
       <c r="B542" s="3" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr"/>
@@ -20067,7 +20067,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr">
@@ -20079,7 +20079,7 @@
     <row r="543" ht="16" customHeight="1">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029250747</t>
+          <t>2-s2.0-105029263427</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="C543" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr"/>
@@ -20103,7 +20103,7 @@
       </c>
       <c r="I543" s="4" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J543" s="4" t="inlineStr">
@@ -20115,7 +20115,7 @@
     <row r="544" ht="16" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029263427</t>
+          <t>2-s2.0-105029346081</t>
         </is>
       </c>
       <c r="B544" s="3" t="n">
@@ -20131,7 +20131,7 @@
       <c r="F544" s="2" t="inlineStr"/>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H544" s="2" t="n">
@@ -20139,19 +20139,19 @@
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="545" ht="16" customHeight="1">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029346081</t>
+          <t>2-s2.0-105029819163</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
@@ -20167,7 +20167,7 @@
       <c r="F545" s="4" t="inlineStr"/>
       <c r="G545" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H545" s="4" t="n">
@@ -20175,19 +20175,19 @@
       </c>
       <c r="I545" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="546" ht="16" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029819163</t>
+          <t>2-s2.0-105029861079</t>
         </is>
       </c>
       <c r="B546" s="3" t="n">
@@ -20203,7 +20203,7 @@
       <c r="F546" s="2" t="inlineStr"/>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H546" s="2" t="n">
@@ -20211,19 +20211,19 @@
       </c>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="547" ht="16" customHeight="1">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029861079</t>
+          <t>2-s2.0-105030266202</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
@@ -20239,7 +20239,7 @@
       <c r="F547" s="4" t="inlineStr"/>
       <c r="G547" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H547" s="4" t="n">
@@ -20247,19 +20247,19 @@
       </c>
       <c r="I547" s="4" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J547" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="548" ht="16" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105030266202</t>
+          <t>2-s2.0-105031262073</t>
         </is>
       </c>
       <c r="B548" s="3" t="n">
@@ -20295,7 +20295,7 @@
     <row r="549" ht="16" customHeight="1">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031262073</t>
+          <t>2-s2.0-105031578343</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
@@ -20311,7 +20311,7 @@
       <c r="F549" s="4" t="inlineStr"/>
       <c r="G549" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H549" s="4" t="n">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="I549" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J549" s="4" t="inlineStr">
@@ -20331,7 +20331,7 @@
     <row r="550" ht="16" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031578343</t>
+          <t>2-s2.0-105031596663</t>
         </is>
       </c>
       <c r="B550" s="3" t="n">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr"/>
@@ -20347,7 +20347,7 @@
       <c r="F550" s="2" t="inlineStr"/>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H550" s="2" t="n">
@@ -20355,19 +20355,19 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="551" ht="16" customHeight="1">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031596663</t>
+          <t>2-s2.0-105033266676</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="C551" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr"/>
@@ -20383,7 +20383,7 @@
       <c r="F551" s="4" t="inlineStr"/>
       <c r="G551" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H551" s="4" t="n">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="I551" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J551" s="4" t="inlineStr">
@@ -20403,7 +20403,7 @@
     <row r="552" ht="16" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033266676</t>
+          <t>2-s2.0-105033689829</t>
         </is>
       </c>
       <c r="B552" s="3" t="n">
@@ -20427,19 +20427,19 @@
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="553" ht="16" customHeight="1">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033689829</t>
+          <t>2-s2.0-105033935110</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="I553" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J553" s="4" t="inlineStr">
@@ -20475,7 +20475,7 @@
     <row r="554" ht="16" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033935110</t>
+          <t>2-s2.0-105033998924</t>
         </is>
       </c>
       <c r="B554" s="3" t="n">
@@ -20491,7 +20491,7 @@
       <c r="F554" s="2" t="inlineStr"/>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H554" s="2" t="n">
@@ -20499,19 +20499,19 @@
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="555" ht="16" customHeight="1">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033998924</t>
+          <t>2-s2.0-105034105140</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
@@ -20527,7 +20527,7 @@
       <c r="F555" s="4" t="inlineStr"/>
       <c r="G555" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H555" s="4" t="n">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="I555" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J555" s="4" t="inlineStr">
@@ -20547,7 +20547,7 @@
     <row r="556" ht="16" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034105140</t>
+          <t>2-s2.0-105034275781</t>
         </is>
       </c>
       <c r="B556" s="3" t="n">
@@ -20571,19 +20571,19 @@
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="557" ht="16" customHeight="1">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034275781</t>
+          <t>2-s2.0-105034300666</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -20599,7 +20599,7 @@
       <c r="F557" s="4" t="inlineStr"/>
       <c r="G557" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H557" s="4" t="n">
@@ -20607,19 +20607,19 @@
       </c>
       <c r="I557" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
         </is>
       </c>
       <c r="J557" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="558" ht="16" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034300666</t>
+          <t>2-s2.0-105034470662</t>
         </is>
       </c>
       <c r="B558" s="3" t="n">
@@ -20635,7 +20635,7 @@
       <c r="F558" s="2" t="inlineStr"/>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H558" s="2" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -20655,7 +20655,7 @@
     <row r="559" ht="16" customHeight="1">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034470662</t>
+          <t>2-s2.0-105034590431</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -20671,7 +20671,7 @@
       <c r="F559" s="4" t="inlineStr"/>
       <c r="G559" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H559" s="4" t="n">
@@ -20679,19 +20679,19 @@
       </c>
       <c r="I559" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J559" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="560" ht="16" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034590431</t>
+          <t>2-s2.0-105035297301</t>
         </is>
       </c>
       <c r="B560" s="3" t="n">
@@ -20715,19 +20715,19 @@
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="561" ht="16" customHeight="1">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035297301</t>
+          <t>2-s2.0-105035301017</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -20751,19 +20751,19 @@
       </c>
       <c r="I561" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J561" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="562" ht="16" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035301017</t>
+          <t>2-s2.0-105035647006</t>
         </is>
       </c>
       <c r="B562" s="3" t="n">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr"/>
@@ -20787,19 +20787,19 @@
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="563" ht="16" customHeight="1">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035647006</t>
+          <t>2-s2.0-105035812865</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="C563" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr"/>
@@ -20815,7 +20815,7 @@
       <c r="F563" s="4" t="inlineStr"/>
       <c r="G563" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H563" s="4" t="n">
@@ -20823,19 +20823,19 @@
       </c>
       <c r="I563" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J563" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="564" ht="16" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035812865</t>
+          <t>2-s2.0-105037520290</t>
         </is>
       </c>
       <c r="B564" s="3" t="n">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr"/>
@@ -20851,7 +20851,7 @@
       <c r="F564" s="2" t="inlineStr"/>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H564" s="2" t="n">
@@ -20859,19 +20859,19 @@
       </c>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="565" ht="16" customHeight="1">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105037520290</t>
+          <t>2-s2.0-105037554330</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C565" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr"/>
@@ -20887,7 +20887,7 @@
       <c r="F565" s="4" t="inlineStr"/>
       <c r="G565" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H565" s="4" t="n">
@@ -20895,19 +20895,19 @@
       </c>
       <c r="I565" s="4" t="inlineStr">
         <is>
-          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J565" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="566" ht="16" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105037554330</t>
+          <t>2-s2.0-105038191517</t>
         </is>
       </c>
       <c r="B566" s="3" t="n">
@@ -20923,7 +20923,7 @@
       <c r="F566" s="2" t="inlineStr"/>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H566" s="2" t="n">
@@ -20931,19 +20931,19 @@
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="567" ht="16" customHeight="1">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038191517</t>
+          <t>2-s2.0-105038213221</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
@@ -20959,7 +20959,7 @@
       <c r="F567" s="4" t="inlineStr"/>
       <c r="G567" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H567" s="4" t="n">
@@ -20967,19 +20967,19 @@
       </c>
       <c r="I567" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J567" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="568" ht="16" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038213221</t>
+          <t>2-s2.0-105038231274</t>
         </is>
       </c>
       <c r="B568" s="3" t="n">
@@ -20995,7 +20995,7 @@
       <c r="F568" s="2" t="inlineStr"/>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H568" s="2" t="n">
@@ -21003,19 +21003,19 @@
       </c>
       <c r="I568" s="2" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="569" ht="16" customHeight="1">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038231274</t>
+          <t>2-s2.0-105038348383</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -21039,19 +21039,19 @@
       </c>
       <c r="I569" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J569" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="570" ht="16" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038348383</t>
+          <t>2-s2.0-105038667034</t>
         </is>
       </c>
       <c r="B570" s="3" t="n">
@@ -21067,7 +21067,7 @@
       <c r="F570" s="2" t="inlineStr"/>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H570" s="2" t="n">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J570" s="2" t="inlineStr">
@@ -21087,7 +21087,7 @@
     <row r="571" ht="16" customHeight="1">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038667034</t>
+          <t>2-s2.0-105040384895</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -21103,7 +21103,7 @@
       <c r="F571" s="4" t="inlineStr"/>
       <c r="G571" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H571" s="4" t="n">
@@ -21111,19 +21111,19 @@
       </c>
       <c r="I571" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J571" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="572" ht="16" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040384895</t>
+          <t>2-s2.0-105040648386</t>
         </is>
       </c>
       <c r="B572" s="3" t="n">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J572" s="2" t="inlineStr">
@@ -21159,7 +21159,7 @@
     <row r="573" ht="16" customHeight="1">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040648386</t>
+          <t>2-s2.0-105040720975</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr"/>
@@ -21175,7 +21175,7 @@
       <c r="F573" s="4" t="inlineStr"/>
       <c r="G573" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H573" s="4" t="n">
@@ -21183,7 +21183,7 @@
       </c>
       <c r="I573" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J573" s="4" t="inlineStr">
@@ -21195,7 +21195,7 @@
     <row r="574" ht="16" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040720975</t>
+          <t>2-s2.0-105040813266</t>
         </is>
       </c>
       <c r="B574" s="3" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr"/>
@@ -21211,7 +21211,7 @@
       <c r="F574" s="2" t="inlineStr"/>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H574" s="2" t="n">
@@ -21219,19 +21219,19 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="575" ht="16" customHeight="1">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040813266</t>
+          <t>2-s2.0-105040833810</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -21255,19 +21255,19 @@
       </c>
       <c r="I575" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J575" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="576" ht="16" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040833810</t>
+          <t>2-s2.0-105040999318</t>
         </is>
       </c>
       <c r="B576" s="3" t="n">
@@ -21283,7 +21283,7 @@
       <c r="F576" s="2" t="inlineStr"/>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H576" s="2" t="n">
@@ -21291,19 +21291,19 @@
       </c>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="577" ht="16" customHeight="1">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040999318</t>
+          <t>2-s2.0-105041019868</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
@@ -21319,7 +21319,7 @@
       <c r="F577" s="4" t="inlineStr"/>
       <c r="G577" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H577" s="4" t="n">
@@ -21327,19 +21327,19 @@
       </c>
       <c r="I577" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="J577" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="578" ht="16" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041019868</t>
+          <t>2-s2.0-105041022111</t>
         </is>
       </c>
       <c r="B578" s="3" t="n">
@@ -21355,7 +21355,7 @@
       <c r="F578" s="2" t="inlineStr"/>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H578" s="2" t="n">
@@ -21363,19 +21363,19 @@
       </c>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="579" ht="16" customHeight="1">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041022111</t>
+          <t>2-s2.0-105041142576</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -21391,7 +21391,7 @@
       <c r="F579" s="4" t="inlineStr"/>
       <c r="G579" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H579" s="4" t="n">
@@ -21399,19 +21399,19 @@
       </c>
       <c r="I579" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J579" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="580" ht="16" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041142576</t>
+          <t>2-s2.0-105041927617</t>
         </is>
       </c>
       <c r="B580" s="3" t="n">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr"/>
@@ -21427,7 +21427,7 @@
       <c r="F580" s="2" t="inlineStr"/>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H580" s="2" t="n">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J580" s="2" t="inlineStr">
@@ -21447,7 +21447,7 @@
     <row r="581" ht="16" customHeight="1">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041927617</t>
+          <t>2-s2.0-105042109693</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -21455,7 +21455,7 @@
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr"/>
@@ -21463,7 +21463,7 @@
       <c r="F581" s="4" t="inlineStr"/>
       <c r="G581" s="4" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H581" s="4" t="n">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="I581" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J581" s="4" t="inlineStr">
@@ -21483,7 +21483,7 @@
     <row r="582" ht="16" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042109693</t>
+          <t>2-s2.0-105042557607</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr">
@@ -21519,7 +21519,7 @@
     <row r="583" ht="16" customHeight="1">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105042557607</t>
+          <t>2-s2.0-105042877513</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="I583" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J583" s="4" t="inlineStr">
@@ -21555,7 +21555,7 @@
     <row r="584" ht="16" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042877513</t>
+          <t>2-s2.0-105043654106</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr">
@@ -21591,7 +21591,7 @@
     <row r="585" ht="16" customHeight="1">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105043654106</t>
+          <t>2-s2.0-105044659449</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -21607,7 +21607,7 @@
       <c r="F585" s="4" t="inlineStr"/>
       <c r="G585" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H585" s="4" t="n">
@@ -21615,19 +21615,19 @@
       </c>
       <c r="I585" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="J585" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="586" ht="16" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105044659449</t>
+          <t>2-s2.0-105044663806</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
@@ -21651,19 +21651,19 @@
       </c>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="587" ht="16" customHeight="1">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044663806</t>
+          <t>2-s2.0-105044699156</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="I587" s="4" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J587" s="4" t="inlineStr">
@@ -21699,7 +21699,7 @@
     <row r="588" ht="16" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105044699156</t>
+          <t>2-s2.0-105044735313</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
@@ -21715,7 +21715,7 @@
       <c r="F588" s="2" t="inlineStr"/>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H588" s="2" t="n">
@@ -21723,19 +21723,19 @@
       </c>
       <c r="I588" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="589" ht="16" customHeight="1">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044735313</t>
+          <t>2-s2.0-105045219323</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -21751,7 +21751,7 @@
       <c r="F589" s="4" t="inlineStr"/>
       <c r="G589" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H589" s="4" t="n">
@@ -21759,19 +21759,19 @@
       </c>
       <c r="I589" s="4" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J589" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="590" ht="16" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105045219323</t>
+          <t>2-s2.0-105045424298</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
@@ -21787,7 +21787,7 @@
       <c r="F590" s="2" t="inlineStr"/>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H590" s="2" t="n">
@@ -21807,7 +21807,7 @@
     <row r="591" ht="16" customHeight="1">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105045927756</t>
+          <t>2-s2.0-105045743544</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="C591" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D591" s="4" t="inlineStr"/>
@@ -21831,17 +21831,161 @@
       </c>
       <c r="I591" s="4" t="inlineStr">
         <is>
+          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
+        </is>
+      </c>
+      <c r="J591" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="16" customHeight="1">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105045927756</t>
+        </is>
+      </c>
+      <c r="B592" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C592" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr"/>
+      <c r="E592" s="3" t="inlineStr"/>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
           <t>Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
-      <c r="J591" s="4" t="inlineStr">
+      <c r="J592" s="2" t="inlineStr">
         <is>
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
+    <row r="593" ht="16" customHeight="1">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047004470</t>
+        </is>
+      </c>
+      <c r="B593" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D593" s="4" t="inlineStr"/>
+      <c r="E593" s="5" t="inlineStr"/>
+      <c r="F593" s="4" t="inlineStr"/>
+      <c r="G593" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H593" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I593" s="4" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J593" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="16" customHeight="1">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047128367</t>
+        </is>
+      </c>
+      <c r="B594" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C594" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr"/>
+      <c r="E594" s="3" t="inlineStr"/>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="16" customHeight="1">
+      <c r="A595" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047180719</t>
+        </is>
+      </c>
+      <c r="B595" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D595" s="4" t="inlineStr"/>
+      <c r="E595" s="5" t="inlineStr"/>
+      <c r="F595" s="4" t="inlineStr"/>
+      <c r="G595" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H595" s="4" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I595" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Luis del Rio Cortina</t>
+        </is>
+      </c>
+      <c r="J595" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J591"/>
+  <autoFilter ref="A1:J595"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21852,7 +21996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J591"/>
+  <dimension ref="A1:J595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -38888,7 +39032,7 @@
     <row r="501" ht="16" customHeight="1">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105045743544</t>
+          <t>2-s2.0-85184473223</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
@@ -38904,25 +39048,25 @@
       <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H501" s="4" t="inlineStr"/>
       <c r="I501" s="4" t="inlineStr">
         <is>
-          <t>Pedro Vazquez Miraz</t>
+          <t>Jeovanny de Jesus Muentes Acevedo</t>
         </is>
       </c>
       <c r="J501" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="502" ht="16" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85184473223</t>
+          <t>2-s2.0-85196638440</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
@@ -38944,19 +39088,19 @@
       <c r="H502" s="2" t="inlineStr"/>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>Jeovanny de Jesus Muentes Acevedo</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="503" ht="16" customHeight="1">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85196638440</t>
+          <t>2-s2.0-85203247315</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
@@ -38964,7 +39108,7 @@
       </c>
       <c r="C503" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr"/>
@@ -38978,19 +39122,19 @@
       <c r="H503" s="4" t="inlineStr"/>
       <c r="I503" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J503" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="504" ht="16" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85203247315</t>
+          <t>2-s2.0-85204485969</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
@@ -38998,7 +39142,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr"/>
@@ -39012,7 +39156,7 @@
       <c r="H504" s="2" t="inlineStr"/>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -39024,7 +39168,7 @@
     <row r="505" ht="16" customHeight="1">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85204485969</t>
+          <t>2-s2.0-85204899789</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
@@ -39040,25 +39184,25 @@
       <c r="F505" s="4" t="inlineStr"/>
       <c r="G505" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H505" s="4" t="inlineStr"/>
       <c r="I505" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>James Manuel Perez Moron</t>
         </is>
       </c>
       <c r="J505" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="506" ht="16" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85204899789</t>
+          <t>2-s2.0-85207831270</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
@@ -39066,7 +39210,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr"/>
@@ -39074,25 +39218,25 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr"/>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>James Manuel Perez Moron</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85207831270</t>
+          <t>2-s2.0-85207842768</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
@@ -39114,7 +39258,7 @@
       <c r="H507" s="4" t="inlineStr"/>
       <c r="I507" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J507" s="4" t="inlineStr">
@@ -39126,7 +39270,7 @@
     <row r="508" ht="16" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85207842768</t>
+          <t>2-s2.0-85208015450</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
@@ -39148,7 +39292,7 @@
       <c r="H508" s="2" t="inlineStr"/>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -39160,7 +39304,7 @@
     <row r="509" ht="16" customHeight="1">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85208015450</t>
+          <t>2-s2.0-85208026562</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
@@ -39182,7 +39326,7 @@
       <c r="H509" s="4" t="inlineStr"/>
       <c r="I509" s="4" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J509" s="4" t="inlineStr">
@@ -39194,7 +39338,7 @@
     <row r="510" ht="16" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85208026562</t>
+          <t>2-s2.0-85209250813</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
@@ -39202,7 +39346,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr"/>
@@ -39210,25 +39354,25 @@
       <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="511" ht="16" customHeight="1">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85209250813</t>
+          <t>2-s2.0-85212267636</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
@@ -39250,19 +39394,19 @@
       <c r="H511" s="4" t="inlineStr"/>
       <c r="I511" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J511" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="512" ht="16" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85212267636</t>
+          <t>2-s2.0-85212831235</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
@@ -39278,13 +39422,13 @@
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr"/>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -39296,7 +39440,7 @@
     <row r="513" ht="16" customHeight="1">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85212831235</t>
+          <t>2-s2.0-85213079490</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
@@ -39312,25 +39456,25 @@
       <c r="F513" s="4" t="inlineStr"/>
       <c r="G513" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H513" s="4" t="inlineStr"/>
       <c r="I513" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J513" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="514" ht="16" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079490</t>
+          <t>2-s2.0-85213079633</t>
         </is>
       </c>
       <c r="B514" s="3" t="n">
@@ -39346,25 +39490,25 @@
       <c r="F514" s="2" t="inlineStr"/>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr"/>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="515" ht="16" customHeight="1">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85213079633</t>
+          <t>2-s2.0-85213083915</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
@@ -39386,19 +39530,19 @@
       <c r="H515" s="4" t="inlineStr"/>
       <c r="I515" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J515" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="516" ht="16" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85213083915</t>
+          <t>2-s2.0-85214707412</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
@@ -39432,7 +39576,7 @@
     <row r="517" ht="16" customHeight="1">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85214707412</t>
+          <t>2-s2.0-85215238378</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
@@ -39448,13 +39592,13 @@
       <c r="F517" s="4" t="inlineStr"/>
       <c r="G517" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H517" s="4" t="inlineStr"/>
       <c r="I517" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J517" s="4" t="inlineStr">
@@ -39466,7 +39610,7 @@
     <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85215238378</t>
+          <t>2-s2.0-85215371893</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">
@@ -39482,25 +39626,25 @@
       <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="519" ht="16" customHeight="1">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85215371893</t>
+          <t>2-s2.0-85218385938</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -39508,7 +39652,7 @@
       </c>
       <c r="C519" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr"/>
@@ -39516,25 +39660,25 @@
       <c r="F519" s="4" t="inlineStr"/>
       <c r="G519" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H519" s="4" t="inlineStr"/>
       <c r="I519" s="4" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J519" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="520" ht="16" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-85218385938</t>
+          <t>2-s2.0-85219053945</t>
         </is>
       </c>
       <c r="B520" s="3" t="n">
@@ -39542,7 +39686,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr"/>
@@ -39550,25 +39694,25 @@
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr"/>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="521" ht="16" customHeight="1">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-85219053945</t>
+          <t>2-s2.0-86000303183</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -39584,13 +39728,13 @@
       <c r="F521" s="4" t="inlineStr"/>
       <c r="G521" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H521" s="4" t="inlineStr"/>
       <c r="I521" s="4" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="J521" s="4" t="inlineStr">
@@ -39602,7 +39746,7 @@
     <row r="522" ht="16" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000303183</t>
+          <t>2-s2.0-86000354258</t>
         </is>
       </c>
       <c r="B522" s="3" t="n">
@@ -39624,7 +39768,7 @@
       <c r="H522" s="2" t="inlineStr"/>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -39636,7 +39780,7 @@
     <row r="523" ht="16" customHeight="1">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-86000354258</t>
+          <t>2-s2.0-86000451627</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -39644,7 +39788,7 @@
       </c>
       <c r="C523" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr"/>
@@ -39658,27 +39802,27 @@
       <c r="H523" s="4" t="inlineStr"/>
       <c r="I523" s="4" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J523" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="524" ht="16" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-86000451627</t>
+          <t>2-s2.0-105007361101</t>
         </is>
       </c>
       <c r="B524" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr"/>
@@ -39686,13 +39830,13 @@
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr"/>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -39704,7 +39848,7 @@
     <row r="525" ht="16" customHeight="1">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105007361101</t>
+          <t>2-s2.0-105013662781</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
@@ -39726,19 +39870,19 @@
       <c r="H525" s="4" t="inlineStr"/>
       <c r="I525" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J525" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="526" ht="16" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105013662781</t>
+          <t>2-s2.0-105016249780</t>
         </is>
       </c>
       <c r="B526" s="3" t="n">
@@ -39746,7 +39890,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr"/>
@@ -39754,25 +39898,25 @@
       <c r="F526" s="2" t="inlineStr"/>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr"/>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="527" ht="16" customHeight="1">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105016249780</t>
+          <t>2-s2.0-105017763405</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
@@ -39780,7 +39924,7 @@
       </c>
       <c r="C527" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr"/>
@@ -39788,25 +39932,25 @@
       <c r="F527" s="4" t="inlineStr"/>
       <c r="G527" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H527" s="4" t="inlineStr"/>
       <c r="I527" s="4" t="inlineStr">
         <is>
-          <t>Raul Andres Vargas Ramirez; Lenny Alexandra Romero Perez; Sonia Helena Contreras Ortiz</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J527" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="528" ht="16" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105017763405</t>
+          <t>2-s2.0-105020672925</t>
         </is>
       </c>
       <c r="B528" s="3" t="n">
@@ -39814,7 +39958,7 @@
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr"/>
@@ -39822,25 +39966,25 @@
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr"/>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="529" ht="16" customHeight="1">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020672925</t>
+          <t>2-s2.0-105020779857</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
@@ -39862,19 +40006,19 @@
       <c r="H529" s="4" t="inlineStr"/>
       <c r="I529" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
         </is>
       </c>
       <c r="J529" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="530" ht="16" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020779857</t>
+          <t>2-s2.0-105020787948</t>
         </is>
       </c>
       <c r="B530" s="3" t="n">
@@ -39896,19 +40040,19 @@
       <c r="H530" s="2" t="inlineStr"/>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez; Jorge Eliecer Duque Pardo</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="531" ht="16" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105020787948</t>
+          <t>2-s2.0-105020807503</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -39930,7 +40074,7 @@
       <c r="H531" s="4" t="inlineStr"/>
       <c r="I531" s="4" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J531" s="4" t="inlineStr">
@@ -39942,7 +40086,7 @@
     <row r="532" ht="16" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105020807503</t>
+          <t>2-s2.0-105023273177</t>
         </is>
       </c>
       <c r="B532" s="3" t="n">
@@ -39958,13 +40102,13 @@
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H532" s="2" t="inlineStr"/>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos</t>
+          <t>Jairo Enrique Serrano Castañeda</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr">
@@ -39976,7 +40120,7 @@
     <row r="533" ht="16" customHeight="1">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105023273177</t>
+          <t>2-s2.0-105023274545</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -40010,7 +40154,7 @@
     <row r="534" ht="16" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105023274545</t>
+          <t>2-s2.0-105024867073</t>
         </is>
       </c>
       <c r="B534" s="3" t="n">
@@ -40018,7 +40162,7 @@
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr"/>
@@ -40026,25 +40170,25 @@
       <c r="F534" s="2" t="inlineStr"/>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr"/>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>Jairo Enrique Serrano Castañeda</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="535" ht="16" customHeight="1">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105024867073</t>
+          <t>2-s2.0-105027320140</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -40066,19 +40210,19 @@
       <c r="H535" s="4" t="inlineStr"/>
       <c r="I535" s="4" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
         </is>
       </c>
       <c r="J535" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="536" ht="16" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105027320140</t>
+          <t>2-s2.0-105027841808</t>
         </is>
       </c>
       <c r="B536" s="3" t="n">
@@ -40094,13 +40238,13 @@
       <c r="F536" s="2" t="inlineStr"/>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr"/>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>Argemiro Palencia Diaz; Alfredo Miguel Abuchar Curi</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
@@ -40112,7 +40256,7 @@
     <row r="537" ht="16" customHeight="1">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105027841808</t>
+          <t>2-s2.0-105028108336</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
@@ -40120,7 +40264,7 @@
       </c>
       <c r="C537" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr"/>
@@ -40134,19 +40278,19 @@
       <c r="H537" s="4" t="inlineStr"/>
       <c r="I537" s="4" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J537" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="538" ht="16" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028108336</t>
+          <t>2-s2.0-105028439729</t>
         </is>
       </c>
       <c r="B538" s="3" t="n">
@@ -40154,7 +40298,7 @@
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr"/>
@@ -40162,25 +40306,25 @@
       <c r="F538" s="2" t="inlineStr"/>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr"/>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios; Diana Carolina Rubiano Labrador</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="539" ht="16" customHeight="1">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028439729</t>
+          <t>2-s2.0-105028658534</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
@@ -40188,7 +40332,7 @@
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr"/>
@@ -40196,25 +40340,25 @@
       <c r="F539" s="4" t="inlineStr"/>
       <c r="G539" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H539" s="4" t="inlineStr"/>
       <c r="I539" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="J539" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="540" ht="16" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028658534</t>
+          <t>2-s2.0-105028891498</t>
         </is>
       </c>
       <c r="B540" s="3" t="n">
@@ -40222,7 +40366,7 @@
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr"/>
@@ -40230,25 +40374,25 @@
       <c r="F540" s="2" t="inlineStr"/>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr"/>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="541" ht="16" customHeight="1">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105028891498</t>
+          <t>2-s2.0-105028921643</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -40264,25 +40408,25 @@
       <c r="F541" s="4" t="inlineStr"/>
       <c r="G541" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H541" s="4" t="inlineStr"/>
       <c r="I541" s="4" t="inlineStr">
         <is>
-          <t>Humberto Manuel Marbello Peña; David Sierra Porta</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J541" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="542" ht="16" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105028921643</t>
+          <t>2-s2.0-105029250747</t>
         </is>
       </c>
       <c r="B542" s="3" t="n">
@@ -40290,7 +40434,7 @@
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr"/>
@@ -40304,7 +40448,7 @@
       <c r="H542" s="2" t="inlineStr"/>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr">
@@ -40316,7 +40460,7 @@
     <row r="543" ht="16" customHeight="1">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029250747</t>
+          <t>2-s2.0-105029263427</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
@@ -40324,7 +40468,7 @@
       </c>
       <c r="C543" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr"/>
@@ -40338,7 +40482,7 @@
       <c r="H543" s="4" t="inlineStr"/>
       <c r="I543" s="4" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
         </is>
       </c>
       <c r="J543" s="4" t="inlineStr">
@@ -40350,7 +40494,7 @@
     <row r="544" ht="16" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029263427</t>
+          <t>2-s2.0-105029346081</t>
         </is>
       </c>
       <c r="B544" s="3" t="n">
@@ -40366,25 +40510,25 @@
       <c r="F544" s="2" t="inlineStr"/>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H544" s="2" t="inlineStr"/>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>Pablo Gustavo Salomo Abitbol Pineiro</t>
+          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="545" ht="16" customHeight="1">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029346081</t>
+          <t>2-s2.0-105029819163</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
@@ -40400,25 +40544,25 @@
       <c r="F545" s="4" t="inlineStr"/>
       <c r="G545" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H545" s="4" t="inlineStr"/>
       <c r="I545" s="4" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel; Pedro Vazquez Miraz</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="546" ht="16" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105029819163</t>
+          <t>2-s2.0-105029861079</t>
         </is>
       </c>
       <c r="B546" s="3" t="n">
@@ -40434,25 +40578,25 @@
       <c r="F546" s="2" t="inlineStr"/>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr"/>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Lina Margarita Marrugo Salas</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="547" ht="16" customHeight="1">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105029861079</t>
+          <t>2-s2.0-105030266202</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
@@ -40474,19 +40618,19 @@
       <c r="H547" s="4" t="inlineStr"/>
       <c r="I547" s="4" t="inlineStr">
         <is>
-          <t>Lina Margarita Marrugo Salas</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J547" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="548" ht="16" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105030266202</t>
+          <t>2-s2.0-105031262073</t>
         </is>
       </c>
       <c r="B548" s="3" t="n">
@@ -40502,7 +40646,7 @@
       <c r="F548" s="2" t="inlineStr"/>
       <c r="G548" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H548" s="2" t="inlineStr"/>
@@ -40520,7 +40664,7 @@
     <row r="549" ht="16" customHeight="1">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031262073</t>
+          <t>2-s2.0-105031578343</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
@@ -40536,13 +40680,13 @@
       <c r="F549" s="4" t="inlineStr"/>
       <c r="G549" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H549" s="4" t="inlineStr"/>
       <c r="I549" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J549" s="4" t="inlineStr">
@@ -40554,7 +40698,7 @@
     <row r="550" ht="16" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105031578343</t>
+          <t>2-s2.0-105031596663</t>
         </is>
       </c>
       <c r="B550" s="3" t="n">
@@ -40562,7 +40706,7 @@
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr"/>
@@ -40570,25 +40714,25 @@
       <c r="F550" s="2" t="inlineStr"/>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H550" s="2" t="inlineStr"/>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="551" ht="16" customHeight="1">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105031596663</t>
+          <t>2-s2.0-105033266676</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
@@ -40596,7 +40740,7 @@
       </c>
       <c r="C551" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr"/>
@@ -40610,7 +40754,7 @@
       <c r="H551" s="4" t="inlineStr"/>
       <c r="I551" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Claudia Patricia Diaz Mendoza</t>
         </is>
       </c>
       <c r="J551" s="4" t="inlineStr">
@@ -40622,7 +40766,7 @@
     <row r="552" ht="16" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033266676</t>
+          <t>2-s2.0-105033689829</t>
         </is>
       </c>
       <c r="B552" s="3" t="n">
@@ -40638,25 +40782,25 @@
       <c r="F552" s="2" t="inlineStr"/>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H552" s="2" t="inlineStr"/>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="553" ht="16" customHeight="1">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033689829</t>
+          <t>2-s2.0-105033935110</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -40672,13 +40816,13 @@
       <c r="F553" s="4" t="inlineStr"/>
       <c r="G553" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H553" s="4" t="inlineStr"/>
       <c r="I553" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J553" s="4" t="inlineStr">
@@ -40690,7 +40834,7 @@
     <row r="554" ht="16" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105033935110</t>
+          <t>2-s2.0-105033998924</t>
         </is>
       </c>
       <c r="B554" s="3" t="n">
@@ -40712,19 +40856,19 @@
       <c r="H554" s="2" t="inlineStr"/>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="555" ht="16" customHeight="1">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105033998924</t>
+          <t>2-s2.0-105034105140</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
@@ -40746,7 +40890,7 @@
       <c r="H555" s="4" t="inlineStr"/>
       <c r="I555" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="J555" s="4" t="inlineStr">
@@ -40758,7 +40902,7 @@
     <row r="556" ht="16" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034105140</t>
+          <t>2-s2.0-105034275781</t>
         </is>
       </c>
       <c r="B556" s="3" t="n">
@@ -40774,25 +40918,25 @@
       <c r="F556" s="2" t="inlineStr"/>
       <c r="G556" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H556" s="2" t="inlineStr"/>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="557" ht="16" customHeight="1">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034275781</t>
+          <t>2-s2.0-105034300666</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -40814,19 +40958,19 @@
       <c r="H557" s="4" t="inlineStr"/>
       <c r="I557" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
         </is>
       </c>
       <c r="J557" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="558" ht="16" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034300666</t>
+          <t>2-s2.0-105034470662</t>
         </is>
       </c>
       <c r="B558" s="3" t="n">
@@ -40842,13 +40986,13 @@
       <c r="F558" s="2" t="inlineStr"/>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr"/>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>Claudia Patricia Diaz Mendoza; Jorgelina Cecilia Pasqualino</t>
+          <t>Juan Gabriel Fajardo Cuadro</t>
         </is>
       </c>
       <c r="J558" s="2" t="inlineStr">
@@ -40860,7 +41004,7 @@
     <row r="559" ht="16" customHeight="1">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105034470662</t>
+          <t>2-s2.0-105034590431</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -40876,25 +41020,25 @@
       <c r="F559" s="4" t="inlineStr"/>
       <c r="G559" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H559" s="4" t="inlineStr"/>
       <c r="I559" s="4" t="inlineStr">
         <is>
-          <t>Juan Gabriel Fajardo Cuadro</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J559" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="560" ht="16" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105034590431</t>
+          <t>2-s2.0-105035297301</t>
         </is>
       </c>
       <c r="B560" s="3" t="n">
@@ -40916,19 +41060,19 @@
       <c r="H560" s="2" t="inlineStr"/>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="561" ht="16" customHeight="1">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035297301</t>
+          <t>2-s2.0-105035301017</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -40950,19 +41094,19 @@
       <c r="H561" s="4" t="inlineStr"/>
       <c r="I561" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta; Miguel Efren Garces Prettel</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J561" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="562" ht="16" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035301017</t>
+          <t>2-s2.0-105035647006</t>
         </is>
       </c>
       <c r="B562" s="3" t="n">
@@ -40970,7 +41114,7 @@
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr"/>
@@ -40978,25 +41122,25 @@
       <c r="F562" s="2" t="inlineStr"/>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr"/>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="563" ht="16" customHeight="1">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105035647006</t>
+          <t>2-s2.0-105035812865</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -41004,7 +41148,7 @@
       </c>
       <c r="C563" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr"/>
@@ -41018,19 +41162,19 @@
       <c r="H563" s="4" t="inlineStr"/>
       <c r="I563" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J563" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="564" ht="16" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105035812865</t>
+          <t>2-s2.0-105037520290</t>
         </is>
       </c>
       <c r="B564" s="3" t="n">
@@ -41038,7 +41182,7 @@
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr"/>
@@ -41046,25 +41190,25 @@
       <c r="F564" s="2" t="inlineStr"/>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr"/>
       <c r="I564" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
         </is>
       </c>
       <c r="J564" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="565" ht="16" customHeight="1">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105037520290</t>
+          <t>2-s2.0-105037554330</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
@@ -41072,7 +41216,7 @@
       </c>
       <c r="C565" s="5" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr"/>
@@ -41080,25 +41224,25 @@
       <c r="F565" s="4" t="inlineStr"/>
       <c r="G565" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H565" s="4" t="inlineStr"/>
       <c r="I565" s="4" t="inlineStr">
         <is>
-          <t>Andres Guillermo Marrugo Hernandez; Lenny Alexandra Romero Perez</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J565" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas; Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="566" ht="16" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105037554330</t>
+          <t>2-s2.0-105038191517</t>
         </is>
       </c>
       <c r="B566" s="3" t="n">
@@ -41114,25 +41258,25 @@
       <c r="F566" s="2" t="inlineStr"/>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H566" s="2" t="inlineStr"/>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="567" ht="16" customHeight="1">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038191517</t>
+          <t>2-s2.0-105038213221</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
@@ -41154,19 +41298,19 @@
       <c r="H567" s="4" t="inlineStr"/>
       <c r="I567" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="J567" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="568" ht="16" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038213221</t>
+          <t>2-s2.0-105038231274</t>
         </is>
       </c>
       <c r="B568" s="3" t="n">
@@ -41182,25 +41326,25 @@
       <c r="F568" s="2" t="inlineStr"/>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr"/>
       <c r="I568" s="2" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J568" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="569" ht="16" customHeight="1">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038231274</t>
+          <t>2-s2.0-105038348383</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -41222,19 +41366,19 @@
       <c r="H569" s="4" t="inlineStr"/>
       <c r="I569" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Karol Patricia Gutierrez Ruiz</t>
         </is>
       </c>
       <c r="J569" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="570" ht="16" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105038348383</t>
+          <t>2-s2.0-105038667034</t>
         </is>
       </c>
       <c r="B570" s="3" t="n">
@@ -41250,13 +41394,13 @@
       <c r="F570" s="2" t="inlineStr"/>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr"/>
       <c r="I570" s="2" t="inlineStr">
         <is>
-          <t>Karol Patricia Gutierrez Ruiz</t>
+          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
         </is>
       </c>
       <c r="J570" s="2" t="inlineStr">
@@ -41268,7 +41412,7 @@
     <row r="571" ht="16" customHeight="1">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105038667034</t>
+          <t>2-s2.0-105040384895</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -41284,25 +41428,25 @@
       <c r="F571" s="4" t="inlineStr"/>
       <c r="G571" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H571" s="4" t="inlineStr"/>
       <c r="I571" s="4" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro; Pedro Vazquez Miraz</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J571" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="572" ht="16" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040384895</t>
+          <t>2-s2.0-105040648386</t>
         </is>
       </c>
       <c r="B572" s="3" t="n">
@@ -41324,7 +41468,7 @@
       <c r="H572" s="2" t="inlineStr"/>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Yady Tatiana Solano Correa</t>
         </is>
       </c>
       <c r="J572" s="2" t="inlineStr">
@@ -41336,7 +41480,7 @@
     <row r="573" ht="16" customHeight="1">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040648386</t>
+          <t>2-s2.0-105040720975</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -41344,7 +41488,7 @@
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr"/>
@@ -41352,13 +41496,13 @@
       <c r="F573" s="4" t="inlineStr"/>
       <c r="G573" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>No Q</t>
         </is>
       </c>
       <c r="H573" s="4" t="inlineStr"/>
       <c r="I573" s="4" t="inlineStr">
         <is>
-          <t>Yady Tatiana Solano Correa</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J573" s="4" t="inlineStr">
@@ -41370,7 +41514,7 @@
     <row r="574" ht="16" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040720975</t>
+          <t>2-s2.0-105040813266</t>
         </is>
       </c>
       <c r="B574" s="3" t="n">
@@ -41378,7 +41522,7 @@
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr"/>
@@ -41386,25 +41530,25 @@
       <c r="F574" s="2" t="inlineStr"/>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>No Q</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H574" s="2" t="inlineStr"/>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Rosa Leonor Acevedo Barrios</t>
         </is>
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="575" ht="16" customHeight="1">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040813266</t>
+          <t>2-s2.0-105040833810</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -41420,25 +41564,25 @@
       <c r="F575" s="4" t="inlineStr"/>
       <c r="G575" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H575" s="4" t="inlineStr"/>
       <c r="I575" s="4" t="inlineStr">
         <is>
-          <t>Rosa Leonor Acevedo Barrios</t>
+          <t>Miguel Efren Garces Prettel</t>
         </is>
       </c>
       <c r="J575" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="576" ht="16" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105040833810</t>
+          <t>2-s2.0-105040999318</t>
         </is>
       </c>
       <c r="B576" s="3" t="n">
@@ -41454,25 +41598,25 @@
       <c r="F576" s="2" t="inlineStr"/>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr"/>
       <c r="I576" s="2" t="inlineStr">
         <is>
-          <t>Miguel Efren Garces Prettel</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="577" ht="16" customHeight="1">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105040999318</t>
+          <t>2-s2.0-105041019868</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
@@ -41488,25 +41632,25 @@
       <c r="F577" s="4" t="inlineStr"/>
       <c r="G577" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H577" s="4" t="inlineStr"/>
       <c r="I577" s="4" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="J577" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="578" ht="16" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041019868</t>
+          <t>2-s2.0-105041022111</t>
         </is>
       </c>
       <c r="B578" s="3" t="n">
@@ -41528,19 +41672,19 @@
       <c r="H578" s="2" t="inlineStr"/>
       <c r="I578" s="2" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Diana Carolina Rubiano Labrador</t>
         </is>
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Ciencias Básicas</t>
         </is>
       </c>
     </row>
     <row r="579" ht="16" customHeight="1">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041022111</t>
+          <t>2-s2.0-105041142576</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -41556,25 +41700,25 @@
       <c r="F579" s="4" t="inlineStr"/>
       <c r="G579" s="4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H579" s="4" t="inlineStr"/>
       <c r="I579" s="4" t="inlineStr">
         <is>
-          <t>Diana Carolina Rubiano Labrador</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J579" s="4" t="inlineStr">
         <is>
-          <t>Ciencias Básicas</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="580" ht="16" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105041142576</t>
+          <t>2-s2.0-105041927617</t>
         </is>
       </c>
       <c r="B580" s="3" t="n">
@@ -41582,7 +41726,7 @@
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr"/>
@@ -41590,13 +41734,13 @@
       <c r="F580" s="2" t="inlineStr"/>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H580" s="2" t="inlineStr"/>
       <c r="I580" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J580" s="2" t="inlineStr">
@@ -41608,7 +41752,7 @@
     <row r="581" ht="16" customHeight="1">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105041927617</t>
+          <t>2-s2.0-105042109693</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -41616,7 +41760,7 @@
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr"/>
@@ -41624,13 +41768,13 @@
       <c r="F581" s="4" t="inlineStr"/>
       <c r="G581" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H581" s="4" t="inlineStr"/>
       <c r="I581" s="4" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
         </is>
       </c>
       <c r="J581" s="4" t="inlineStr">
@@ -41642,7 +41786,7 @@
     <row r="582" ht="16" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042109693</t>
+          <t>2-s2.0-105042557607</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
@@ -41664,7 +41808,7 @@
       <c r="H582" s="2" t="inlineStr"/>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Martinez Santos; Edwin Alexander Puertas del Castillo</t>
+          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr">
@@ -41676,7 +41820,7 @@
     <row r="583" ht="16" customHeight="1">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105042557607</t>
+          <t>2-s2.0-105042877513</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -41692,13 +41836,13 @@
       <c r="F583" s="4" t="inlineStr"/>
       <c r="G583" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H583" s="4" t="inlineStr"/>
       <c r="I583" s="4" t="inlineStr">
         <is>
-          <t>Edwin Alexander Puertas del Castillo; Juan Carlos Martinez Santos</t>
+          <t>Cesar Augusto Viloria Nuñez</t>
         </is>
       </c>
       <c r="J583" s="4" t="inlineStr">
@@ -41710,7 +41854,7 @@
     <row r="584" ht="16" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105042877513</t>
+          <t>2-s2.0-105043654106</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
@@ -41726,13 +41870,13 @@
       <c r="F584" s="2" t="inlineStr"/>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr"/>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>Cesar Augusto Viloria Nuñez</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr">
@@ -41744,7 +41888,7 @@
     <row r="585" ht="16" customHeight="1">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105043654106</t>
+          <t>2-s2.0-105044659449</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -41760,25 +41904,25 @@
       <c r="F585" s="4" t="inlineStr"/>
       <c r="G585" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="H585" s="4" t="inlineStr"/>
       <c r="I585" s="4" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="J585" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
     <row r="586" ht="16" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105044659449</t>
+          <t>2-s2.0-105044663806</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
@@ -41800,19 +41944,19 @@
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Tania Lucia Cobos Cobos</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="587" ht="16" customHeight="1">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044663806</t>
+          <t>2-s2.0-105044699156</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -41834,7 +41978,7 @@
       <c r="H587" s="4" t="inlineStr"/>
       <c r="I587" s="4" t="inlineStr">
         <is>
-          <t>Tania Lucia Cobos Cobos</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J587" s="4" t="inlineStr">
@@ -41846,7 +41990,7 @@
     <row r="588" ht="16" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105044699156</t>
+          <t>2-s2.0-105044735313</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
@@ -41862,25 +42006,25 @@
       <c r="F588" s="2" t="inlineStr"/>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr">
         <is>
-          <t>David Sierra Porta</t>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
         </is>
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>Escuela de Transformación Digital</t>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
     <row r="589" ht="16" customHeight="1">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105044735313</t>
+          <t>2-s2.0-105045219323</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -41896,25 +42040,25 @@
       <c r="F589" s="4" t="inlineStr"/>
       <c r="G589" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H589" s="4" t="inlineStr"/>
       <c r="I589" s="4" t="inlineStr">
         <is>
-          <t>Elsy Mercedes Dominguez de la Ossa</t>
+          <t>David Sierra Porta</t>
         </is>
       </c>
       <c r="J589" s="4" t="inlineStr">
         <is>
-          <t>Escuela de Negocios, Leyes y Sociedad</t>
+          <t>Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
     <row r="590" ht="16" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>2-s2.0-105045219323</t>
+          <t>2-s2.0-105045424298</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
@@ -41948,7 +42092,7 @@
     <row r="591" ht="16" customHeight="1">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>2-s2.0-105045927756</t>
+          <t>2-s2.0-105045743544</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -41956,7 +42100,7 @@
       </c>
       <c r="C591" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D591" s="4" t="inlineStr"/>
@@ -41964,23 +42108,159 @@
       <c r="F591" s="4" t="inlineStr"/>
       <c r="G591" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H591" s="4" t="inlineStr"/>
       <c r="I591" s="4" t="inlineStr">
         <is>
+          <t>Maria Fernanda Medina Reyes; Pedro Vazquez Miraz</t>
+        </is>
+      </c>
+      <c r="J591" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad; Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="16" customHeight="1">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105045927756</t>
+        </is>
+      </c>
+      <c r="B592" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C592" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr"/>
+      <c r="E592" s="3" t="inlineStr"/>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr"/>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
           <t>Andres Guillermo Marrugo Hernandez</t>
         </is>
       </c>
-      <c r="J591" s="4" t="inlineStr">
+      <c r="J592" s="2" t="inlineStr">
         <is>
           <t>Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
+    <row r="593" ht="16" customHeight="1">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047004470</t>
+        </is>
+      </c>
+      <c r="B593" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D593" s="4" t="inlineStr"/>
+      <c r="E593" s="5" t="inlineStr"/>
+      <c r="F593" s="4" t="inlineStr"/>
+      <c r="G593" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H593" s="4" t="inlineStr"/>
+      <c r="I593" s="4" t="inlineStr">
+        <is>
+          <t>David Sierra Porta</t>
+        </is>
+      </c>
+      <c r="J593" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Transformación Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="16" customHeight="1">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047128367</t>
+        </is>
+      </c>
+      <c r="B594" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C594" s="3" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr"/>
+      <c r="E594" s="3" t="inlineStr"/>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr"/>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>Elsy Mercedes Dominguez de la Ossa</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="16" customHeight="1">
+      <c r="A595" s="4" t="inlineStr">
+        <is>
+          <t>2-s2.0-105047180719</t>
+        </is>
+      </c>
+      <c r="B595" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D595" s="4" t="inlineStr"/>
+      <c r="E595" s="5" t="inlineStr"/>
+      <c r="F595" s="4" t="inlineStr"/>
+      <c r="G595" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="H595" s="4" t="inlineStr"/>
+      <c r="I595" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Luis del Rio Cortina</t>
+        </is>
+      </c>
+      <c r="J595" s="4" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios, Leyes y Sociedad</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J591"/>
+  <autoFilter ref="A1:J595"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42224,10 +42504,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>106</v>
@@ -42245,7 +42525,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>3</v>
@@ -42255,12 +42535,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>78.3%</t>
         </is>
       </c>
     </row>
@@ -42271,10 +42551,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>9</v>
@@ -42286,13 +42566,13 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1</v>
@@ -42302,12 +42582,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -42555,10 +42835,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>106</v>
@@ -42573,7 +42853,7 @@
         <v>36</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>15</v>
@@ -42586,12 +42866,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -42602,10 +42882,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>9</v>
@@ -42617,13 +42897,13 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1</v>
@@ -42633,12 +42913,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -42790,10 +43070,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>126</v>
@@ -42805,13 +43085,13 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
@@ -42821,7 +43101,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -42835,10 +43115,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -42850,13 +43130,13 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>18</v>
@@ -42866,7 +43146,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -43156,10 +43436,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>126</v>
@@ -43171,10 +43451,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>33</v>
@@ -43187,7 +43467,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
@@ -43201,10 +43481,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>38</v>
@@ -43216,13 +43496,13 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>46</v>
@@ -43232,7 +43512,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
@@ -43604,19 +43884,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="F5" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>1</v>
@@ -43626,7 +43906,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
